--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -3935,7 +3935,7 @@
         <v>118434958</v>
       </c>
       <c r="B31" t="n">
-        <v>109955</v>
+        <v>109962</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4032,6 +4032,6921 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120382858</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91872</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6047725</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rödfläckig zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>694046</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6360382</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120382859</v>
+      </c>
+      <c r="B33" t="n">
+        <v>86222</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>693938</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6360238</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120382863</v>
+      </c>
+      <c r="B34" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>693842</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6360049</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120382856</v>
+      </c>
+      <c r="B35" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>693985</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6360386</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120382853</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>693992</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6360385</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120382886</v>
+      </c>
+      <c r="B37" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>694010</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6360337</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120382899</v>
+      </c>
+      <c r="B38" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>424</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>694017</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6360293</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120382896</v>
+      </c>
+      <c r="B39" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>424</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>694015</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6360173</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120382861</v>
+      </c>
+      <c r="B40" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>694007</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6360345</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120382854</v>
+      </c>
+      <c r="B41" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>694079</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6360242</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120382135</v>
+      </c>
+      <c r="B42" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>693925</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6360266</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120389982</v>
+      </c>
+      <c r="B43" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vallhagar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>693945</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6360147</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120389981</v>
+      </c>
+      <c r="B44" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vallhagar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>693941</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6360226</v>
+      </c>
+      <c r="S44" t="n">
+        <v>12</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120382845</v>
+      </c>
+      <c r="B45" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>694018</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6360293</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120382864</v>
+      </c>
+      <c r="B46" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>693969</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6360153</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120389970</v>
+      </c>
+      <c r="B47" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>424</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Vallhagar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>693948</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6360161</v>
+      </c>
+      <c r="S47" t="n">
+        <v>11</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120382893</v>
+      </c>
+      <c r="B48" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>693964</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6360133</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120382857</v>
+      </c>
+      <c r="B49" t="n">
+        <v>90351</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>693914</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6360179</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120382901</v>
+      </c>
+      <c r="B50" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>693951</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6360191</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>120382143</v>
+      </c>
+      <c r="B51" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>693925</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6360266</v>
+      </c>
+      <c r="S51" t="n">
+        <v>4</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>120382148</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90021</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>693828</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6360094</v>
+      </c>
+      <c r="S52" t="n">
+        <v>4</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>120382848</v>
+      </c>
+      <c r="B53" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>693804</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6360012</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>120389985</v>
+      </c>
+      <c r="B54" t="n">
+        <v>86465</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vallhagar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>693944</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6360120</v>
+      </c>
+      <c r="S54" t="n">
+        <v>12</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>120389974</v>
+      </c>
+      <c r="B55" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hoxelmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>693816</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6360164</v>
+      </c>
+      <c r="S55" t="n">
+        <v>14</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>120382898</v>
+      </c>
+      <c r="B56" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>424</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>694010</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6360337</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>120382147</v>
+      </c>
+      <c r="B57" t="n">
+        <v>90021</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>693925</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6360266</v>
+      </c>
+      <c r="S57" t="n">
+        <v>4</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>120382150</v>
+      </c>
+      <c r="B58" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>693925</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6360266</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>120382894</v>
+      </c>
+      <c r="B59" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>694014</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6360338</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>120382855</v>
+      </c>
+      <c r="B60" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>694007</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6360253</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>120390006</v>
+      </c>
+      <c r="B61" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Vallhagar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>693959</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6360193</v>
+      </c>
+      <c r="S61" t="n">
+        <v>9</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>120389972</v>
+      </c>
+      <c r="B62" t="n">
+        <v>86325</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>433</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Vallhagar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>693952</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6360138</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120389966</v>
+      </c>
+      <c r="B63" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Vallhagar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>693948</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6360161</v>
+      </c>
+      <c r="S63" t="n">
+        <v>11</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120382132</v>
+      </c>
+      <c r="B64" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>693977</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6360060</v>
+      </c>
+      <c r="S64" t="n">
+        <v>4</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120382881</v>
+      </c>
+      <c r="B65" t="n">
+        <v>85676</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4852</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kastanjefjällskivling</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lepiota castanea</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>693945</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6360205</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120382847</v>
+      </c>
+      <c r="B66" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>693960</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6360226</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120382877</v>
+      </c>
+      <c r="B67" t="n">
+        <v>97908</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>694046</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6360376</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120382895</v>
+      </c>
+      <c r="B68" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>693867</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6360109</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120382889</v>
+      </c>
+      <c r="B69" t="n">
+        <v>86367</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>449</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>694010</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6360176</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120390004</v>
+      </c>
+      <c r="B70" t="n">
+        <v>90021</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4188</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Fransig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hoxelmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>693783</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6360146</v>
+      </c>
+      <c r="S70" t="n">
+        <v>8</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120389967</v>
+      </c>
+      <c r="B71" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>424</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Vallhagar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>693946</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6360234</v>
+      </c>
+      <c r="S71" t="n">
+        <v>9</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120382131</v>
+      </c>
+      <c r="B72" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>693828</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6360094</v>
+      </c>
+      <c r="S72" t="n">
+        <v>4</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120382862</v>
+      </c>
+      <c r="B73" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>694014</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6360294</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120389965</v>
+      </c>
+      <c r="B74" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hoxelmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>693783</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6360146</v>
+      </c>
+      <c r="S74" t="n">
+        <v>8</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120382142</v>
+      </c>
+      <c r="B75" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>693925</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6360266</v>
+      </c>
+      <c r="S75" t="n">
+        <v>4</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120389980</v>
+      </c>
+      <c r="B76" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hoxelmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>693909</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6360231</v>
+      </c>
+      <c r="S76" t="n">
+        <v>18</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120389973</v>
+      </c>
+      <c r="B77" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hoxelmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>693812</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6360133</v>
+      </c>
+      <c r="S77" t="n">
+        <v>8</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120390025</v>
+      </c>
+      <c r="B78" t="n">
+        <v>106214</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hoxelmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>693824</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6360149</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120389977</v>
+      </c>
+      <c r="B79" t="n">
+        <v>86417</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hoxelmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>693846</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6360166</v>
+      </c>
+      <c r="S79" t="n">
+        <v>9</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120390026</v>
+      </c>
+      <c r="B80" t="n">
+        <v>106872</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hoxelmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>693824</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6360149</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120382897</v>
+      </c>
+      <c r="B81" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>424</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>693971</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6360459</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120382146</v>
+      </c>
+      <c r="B82" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>693828</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6360094</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120389979</v>
+      </c>
+      <c r="B83" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hoxelmyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>693831</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6360180</v>
+      </c>
+      <c r="S83" t="n">
+        <v>4</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120382876</v>
+      </c>
+      <c r="B84" t="n">
+        <v>97908</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>693968</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6360152</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120389969</v>
+      </c>
+      <c r="B85" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>424</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Vallhagar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>693949</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6360196</v>
+      </c>
+      <c r="S85" t="n">
+        <v>11</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120382891</v>
+      </c>
+      <c r="B86" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>693948</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6360186</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120382136</v>
+      </c>
+      <c r="B87" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>693977</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6360060</v>
+      </c>
+      <c r="S87" t="n">
+        <v>4</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>120382888</v>
+      </c>
+      <c r="B88" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>693806</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6359993</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120382133</v>
+      </c>
+      <c r="B89" t="n">
+        <v>86325</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>433</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>693977</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6360060</v>
+      </c>
+      <c r="S89" t="n">
+        <v>4</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120390005</v>
+      </c>
+      <c r="B90" t="n">
+        <v>90028</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>4191</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Kragjordstjärna</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Geastrum michelianum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Berk. &amp; Broome</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Vallhagar, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>693948</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6360161</v>
+      </c>
+      <c r="S90" t="n">
+        <v>11</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120382900</v>
+      </c>
+      <c r="B91" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>424</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Fröjel Sälle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>693947</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6360230</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120382145</v>
+      </c>
+      <c r="B92" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>694045</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6360164</v>
+      </c>
+      <c r="S92" t="n">
+        <v>6</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120382149</v>
+      </c>
+      <c r="B93" t="n">
+        <v>90060</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>693887</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6360046</v>
+      </c>
+      <c r="S93" t="n">
+        <v>3</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4034,10 +4034,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120382858</v>
+        <v>120382142</v>
       </c>
       <c r="B32" t="n">
-        <v>91872</v>
+        <v>86414</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4050,33 +4050,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6047725</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>694046</v>
+        <v>693925</v>
       </c>
       <c r="R32" t="n">
-        <v>6360382</v>
+        <v>6360266</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4103,30 +4110,39 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4137,10 +4153,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120382859</v>
+        <v>120382856</v>
       </c>
       <c r="B33" t="n">
-        <v>86222</v>
+        <v>86282</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4153,21 +4169,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3762</v>
+        <v>3712</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4177,10 +4193,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693938</v>
+        <v>693985</v>
       </c>
       <c r="R33" t="n">
-        <v>6360238</v>
+        <v>6360386</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4243,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120382863</v>
+        <v>120382899</v>
       </c>
       <c r="B34" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4255,25 +4271,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4283,10 +4299,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>693842</v>
+        <v>694017</v>
       </c>
       <c r="R34" t="n">
-        <v>6360049</v>
+        <v>6360293</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4349,10 +4365,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120382856</v>
+        <v>120382861</v>
       </c>
       <c r="B35" t="n">
-        <v>86282</v>
+        <v>86449</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4361,25 +4377,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4389,10 +4405,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>693985</v>
+        <v>694007</v>
       </c>
       <c r="R35" t="n">
-        <v>6360386</v>
+        <v>6360345</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4455,10 +4471,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120382853</v>
+        <v>120390026</v>
       </c>
       <c r="B36" t="n">
-        <v>57336</v>
+        <v>106872</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4471,34 +4487,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>693992</v>
+        <v>693824</v>
       </c>
       <c r="R36" t="n">
-        <v>6360385</v>
+        <v>6360149</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,9 +4548,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4545,26 +4575,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120382886</v>
+        <v>120389980</v>
       </c>
       <c r="B37" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4573,41 +4599,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>694010</v>
+        <v>693909</v>
       </c>
       <c r="R37" t="n">
-        <v>6360337</v>
+        <v>6360231</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4634,9 +4663,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4651,26 +4690,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120382899</v>
+        <v>120382881</v>
       </c>
       <c r="B38" t="n">
-        <v>86302</v>
+        <v>85676</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4679,25 +4714,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>424</v>
+        <v>4852</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kastanjefjällskivling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Lepiota castanea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4707,10 +4742,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>694017</v>
+        <v>693945</v>
       </c>
       <c r="R38" t="n">
-        <v>6360293</v>
+        <v>6360205</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4773,10 +4808,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120382896</v>
+        <v>120382146</v>
       </c>
       <c r="B39" t="n">
-        <v>86302</v>
+        <v>89236</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4785,41 +4820,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>424</v>
+        <v>245042</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>694015</v>
+        <v>693828</v>
       </c>
       <c r="R39" t="n">
-        <v>6360173</v>
+        <v>6360094</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4846,9 +4884,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,12 +4911,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4879,10 +4927,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120382861</v>
+        <v>120382895</v>
       </c>
       <c r="B40" t="n">
-        <v>86449</v>
+        <v>89236</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4891,25 +4939,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6003295</v>
+        <v>245042</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4919,10 +4967,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>694007</v>
+        <v>693867</v>
       </c>
       <c r="R40" t="n">
-        <v>6360345</v>
+        <v>6360109</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4985,10 +5033,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120382854</v>
+        <v>120382145</v>
       </c>
       <c r="B41" t="n">
-        <v>86282</v>
+        <v>89236</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5001,37 +5049,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3712</v>
+        <v>245042</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>694079</v>
+        <v>694045</v>
       </c>
       <c r="R41" t="n">
-        <v>6360242</v>
+        <v>6360164</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5058,9 +5109,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5075,12 +5136,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5091,10 +5152,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120382135</v>
+        <v>120382889</v>
       </c>
       <c r="B42" t="n">
-        <v>86373</v>
+        <v>86367</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5107,40 +5168,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>693925</v>
+        <v>694010</v>
       </c>
       <c r="R42" t="n">
-        <v>6360266</v>
+        <v>6360176</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5167,19 +5225,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5194,12 +5242,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5210,10 +5258,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120389982</v>
+        <v>120389969</v>
       </c>
       <c r="B43" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5222,25 +5270,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5253,13 +5301,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693945</v>
+        <v>693949</v>
       </c>
       <c r="R43" t="n">
-        <v>6360147</v>
+        <v>6360196</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5288,7 +5336,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5298,7 +5346,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5325,10 +5373,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120389981</v>
+        <v>120382854</v>
       </c>
       <c r="B44" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5337,44 +5385,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>693941</v>
+        <v>694079</v>
       </c>
       <c r="R44" t="n">
-        <v>6360226</v>
+        <v>6360242</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5401,19 +5446,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,22 +5463,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120382845</v>
+        <v>120382900</v>
       </c>
       <c r="B45" t="n">
-        <v>90356</v>
+        <v>86302</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5456,21 +5495,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2015</v>
+        <v>424</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5480,10 +5519,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>694018</v>
+        <v>693947</v>
       </c>
       <c r="R45" t="n">
-        <v>6360293</v>
+        <v>6360230</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5546,10 +5585,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120382864</v>
+        <v>120382901</v>
       </c>
       <c r="B46" t="n">
-        <v>86449</v>
+        <v>86414</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5558,25 +5597,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5586,10 +5625,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693969</v>
+        <v>693951</v>
       </c>
       <c r="R46" t="n">
-        <v>6360153</v>
+        <v>6360191</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5652,10 +5691,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120389970</v>
+        <v>120390006</v>
       </c>
       <c r="B47" t="n">
-        <v>86302</v>
+        <v>90356</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5668,21 +5707,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5695,13 +5734,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>693948</v>
+        <v>693959</v>
       </c>
       <c r="R47" t="n">
-        <v>6360161</v>
+        <v>6360193</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5730,7 +5769,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5740,7 +5779,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5767,10 +5806,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120382893</v>
+        <v>120389972</v>
       </c>
       <c r="B48" t="n">
-        <v>89236</v>
+        <v>86325</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5779,38 +5818,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>245042</v>
+        <v>433</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius caesiocanescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>693964</v>
+        <v>693952</v>
       </c>
       <c r="R48" t="n">
-        <v>6360133</v>
+        <v>6360138</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5840,9 +5882,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5857,26 +5909,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120382857</v>
+        <v>120382847</v>
       </c>
       <c r="B49" t="n">
-        <v>90351</v>
+        <v>90356</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5885,25 +5933,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3215</v>
+        <v>2015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5913,10 +5961,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693914</v>
+        <v>693960</v>
       </c>
       <c r="R49" t="n">
-        <v>6360179</v>
+        <v>6360226</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5979,10 +6027,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120382901</v>
+        <v>120382891</v>
       </c>
       <c r="B50" t="n">
-        <v>86414</v>
+        <v>89236</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5995,21 +6043,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3674</v>
+        <v>245042</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6019,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>693951</v>
+        <v>693948</v>
       </c>
       <c r="R50" t="n">
-        <v>6360191</v>
+        <v>6360186</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6085,7 +6133,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120382143</v>
+        <v>120389981</v>
       </c>
       <c r="B51" t="n">
         <v>86449</v>
@@ -6124,17 +6172,17 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>693925</v>
+        <v>693941</v>
       </c>
       <c r="R51" t="n">
-        <v>6360266</v>
+        <v>6360226</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6163,7 +6211,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6173,7 +6221,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6188,26 +6236,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120382148</v>
+        <v>120382131</v>
       </c>
       <c r="B52" t="n">
-        <v>90021</v>
+        <v>86282</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6220,24 +6264,28 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4188</v>
+        <v>3712</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -6323,10 +6371,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120382848</v>
+        <v>120382143</v>
       </c>
       <c r="B53" t="n">
-        <v>90356</v>
+        <v>86449</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6335,41 +6383,44 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693804</v>
+        <v>693925</v>
       </c>
       <c r="R53" t="n">
-        <v>6360012</v>
+        <v>6360266</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6396,9 +6447,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6413,12 +6474,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6429,10 +6490,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120389985</v>
+        <v>120382857</v>
       </c>
       <c r="B54" t="n">
-        <v>86465</v>
+        <v>90351</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6441,44 +6502,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>248947</v>
+        <v>3215</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693944</v>
+        <v>693914</v>
       </c>
       <c r="R54" t="n">
-        <v>6360120</v>
+        <v>6360179</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6505,19 +6563,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6532,22 +6580,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120389974</v>
+        <v>120382147</v>
       </c>
       <c r="B55" t="n">
-        <v>86373</v>
+        <v>90021</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6556,25 +6608,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>248956</v>
+        <v>4188</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6583,17 +6635,17 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>693816</v>
+        <v>693925</v>
       </c>
       <c r="R55" t="n">
-        <v>6360164</v>
+        <v>6360266</v>
       </c>
       <c r="S55" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6622,7 +6674,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6632,7 +6684,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6647,22 +6699,26 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120382898</v>
+        <v>120390004</v>
       </c>
       <c r="B56" t="n">
-        <v>86302</v>
+        <v>90021</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6671,41 +6727,44 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>424</v>
+        <v>4188</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>694010</v>
+        <v>693783</v>
       </c>
       <c r="R56" t="n">
-        <v>6360337</v>
+        <v>6360146</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6732,9 +6791,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6749,26 +6818,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120382147</v>
+        <v>120382888</v>
       </c>
       <c r="B57" t="n">
-        <v>90021</v>
+        <v>86373</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6777,44 +6842,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4188</v>
+        <v>248956</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693925</v>
+        <v>693806</v>
       </c>
       <c r="R57" t="n">
-        <v>6360266</v>
+        <v>6359993</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6841,19 +6903,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6868,12 +6920,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6884,10 +6936,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120382150</v>
+        <v>120382148</v>
       </c>
       <c r="B58" t="n">
-        <v>90356</v>
+        <v>90021</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6896,25 +6948,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2015</v>
+        <v>4188</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6923,14 +6975,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693925</v>
+        <v>693828</v>
       </c>
       <c r="R58" t="n">
-        <v>6360266</v>
+        <v>6360094</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7003,10 +7055,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120382894</v>
+        <v>120382864</v>
       </c>
       <c r="B59" t="n">
-        <v>89236</v>
+        <v>86449</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7015,25 +7067,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>245042</v>
+        <v>6003295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7043,10 +7095,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>694014</v>
+        <v>693969</v>
       </c>
       <c r="R59" t="n">
-        <v>6360338</v>
+        <v>6360153</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7109,10 +7161,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120382855</v>
+        <v>120382136</v>
       </c>
       <c r="B60" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7121,41 +7173,44 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>694007</v>
+        <v>693977</v>
       </c>
       <c r="R60" t="n">
-        <v>6360253</v>
+        <v>6360060</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7182,9 +7237,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7199,12 +7264,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7215,10 +7280,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120390006</v>
+        <v>120390005</v>
       </c>
       <c r="B61" t="n">
-        <v>90356</v>
+        <v>90028</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7227,25 +7292,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2015</v>
+        <v>4191</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7258,13 +7323,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693959</v>
+        <v>693948</v>
       </c>
       <c r="R61" t="n">
-        <v>6360193</v>
+        <v>6360161</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7293,7 +7358,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7303,7 +7368,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7330,10 +7395,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120389972</v>
+        <v>120389977</v>
       </c>
       <c r="B62" t="n">
-        <v>86325</v>
+        <v>86417</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7342,25 +7407,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>433</v>
+        <v>6037417</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7369,17 +7434,17 @@
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693952</v>
+        <v>693846</v>
       </c>
       <c r="R62" t="n">
-        <v>6360138</v>
+        <v>6360166</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7408,7 +7473,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7418,7 +7483,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7445,7 +7510,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120389966</v>
+        <v>120382855</v>
       </c>
       <c r="B63" t="n">
         <v>86282</v>
@@ -7479,22 +7544,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693948</v>
+        <v>694007</v>
       </c>
       <c r="R63" t="n">
-        <v>6360161</v>
+        <v>6360253</v>
       </c>
       <c r="S63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7521,19 +7583,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7548,22 +7600,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120382132</v>
+        <v>120382876</v>
       </c>
       <c r="B64" t="n">
-        <v>86282</v>
+        <v>97908</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7576,40 +7632,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3712</v>
+        <v>219798</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693977</v>
+        <v>693968</v>
       </c>
       <c r="R64" t="n">
-        <v>6360060</v>
+        <v>6360152</v>
       </c>
       <c r="S64" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7636,19 +7689,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7663,12 +7706,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7679,10 +7722,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120382881</v>
+        <v>120382848</v>
       </c>
       <c r="B65" t="n">
-        <v>85676</v>
+        <v>90356</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7691,25 +7734,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4852</v>
+        <v>2015</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kastanjefjällskivling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lepiota castanea</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7719,10 +7762,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693945</v>
+        <v>693804</v>
       </c>
       <c r="R65" t="n">
-        <v>6360205</v>
+        <v>6360012</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7785,10 +7828,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120382847</v>
+        <v>120382858</v>
       </c>
       <c r="B66" t="n">
-        <v>90356</v>
+        <v>91872</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7797,27 +7840,23 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2015</v>
+        <v>6047725</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7825,10 +7864,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>693960</v>
+        <v>694046</v>
       </c>
       <c r="R66" t="n">
-        <v>6360226</v>
+        <v>6360382</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7869,6 +7908,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7891,10 +7931,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120382877</v>
+        <v>120382853</v>
       </c>
       <c r="B67" t="n">
-        <v>97908</v>
+        <v>57336</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7903,25 +7943,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7931,10 +7971,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>694046</v>
+        <v>693992</v>
       </c>
       <c r="R67" t="n">
-        <v>6360376</v>
+        <v>6360385</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7997,10 +8037,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120382895</v>
+        <v>120382859</v>
       </c>
       <c r="B68" t="n">
-        <v>89236</v>
+        <v>86222</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8013,21 +8053,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>245042</v>
+        <v>3762</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8037,10 +8077,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>693867</v>
+        <v>693938</v>
       </c>
       <c r="R68" t="n">
-        <v>6360109</v>
+        <v>6360238</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8103,10 +8143,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120382889</v>
+        <v>120382886</v>
       </c>
       <c r="B69" t="n">
-        <v>86367</v>
+        <v>86373</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8119,21 +8159,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8146,7 +8186,7 @@
         <v>694010</v>
       </c>
       <c r="R69" t="n">
-        <v>6360176</v>
+        <v>6360337</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8209,10 +8249,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120390004</v>
+        <v>120382896</v>
       </c>
       <c r="B70" t="n">
-        <v>90021</v>
+        <v>86302</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8221,44 +8261,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4188</v>
+        <v>424</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>693783</v>
+        <v>694015</v>
       </c>
       <c r="R70" t="n">
-        <v>6360146</v>
+        <v>6360173</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8285,19 +8322,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8312,22 +8339,26 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120389967</v>
+        <v>120382150</v>
       </c>
       <c r="B71" t="n">
-        <v>86302</v>
+        <v>90356</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8340,21 +8371,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8363,17 +8394,17 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693946</v>
+        <v>693925</v>
       </c>
       <c r="R71" t="n">
-        <v>6360234</v>
+        <v>6360266</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8402,7 +8433,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8412,7 +8443,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8427,22 +8458,26 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120382131</v>
+        <v>120389974</v>
       </c>
       <c r="B72" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8451,48 +8486,44 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vallagar norra, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>693828</v>
+        <v>693816</v>
       </c>
       <c r="R72" t="n">
-        <v>6360094</v>
+        <v>6360164</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8521,7 +8552,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8531,7 +8562,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8546,26 +8577,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120382862</v>
+        <v>120389966</v>
       </c>
       <c r="B73" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8574,41 +8601,44 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>694014</v>
+        <v>693948</v>
       </c>
       <c r="R73" t="n">
-        <v>6360294</v>
+        <v>6360161</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8635,9 +8665,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8652,26 +8692,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120389965</v>
+        <v>120389982</v>
       </c>
       <c r="B74" t="n">
-        <v>86282</v>
+        <v>86449</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8680,25 +8716,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8707,17 +8743,17 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>693783</v>
+        <v>693945</v>
       </c>
       <c r="R74" t="n">
-        <v>6360146</v>
+        <v>6360147</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8746,7 +8782,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8756,7 +8792,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8783,10 +8819,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120382142</v>
+        <v>120389979</v>
       </c>
       <c r="B75" t="n">
-        <v>86414</v>
+        <v>86449</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8795,25 +8831,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8822,14 +8858,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>693925</v>
+        <v>693831</v>
       </c>
       <c r="R75" t="n">
-        <v>6360266</v>
+        <v>6360180</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -8861,7 +8897,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8871,7 +8907,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8886,26 +8922,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120389980</v>
+        <v>120382845</v>
       </c>
       <c r="B76" t="n">
-        <v>86449</v>
+        <v>90356</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8914,44 +8946,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693909</v>
+        <v>694018</v>
       </c>
       <c r="R76" t="n">
-        <v>6360231</v>
+        <v>6360293</v>
       </c>
       <c r="S76" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8978,19 +9007,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9005,22 +9024,26 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120389973</v>
+        <v>120382894</v>
       </c>
       <c r="B77" t="n">
-        <v>86373</v>
+        <v>89236</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9029,44 +9052,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>693812</v>
+        <v>694014</v>
       </c>
       <c r="R77" t="n">
-        <v>6360133</v>
+        <v>6360338</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9093,19 +9113,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9120,22 +9130,26 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120390025</v>
+        <v>120382863</v>
       </c>
       <c r="B78" t="n">
-        <v>106214</v>
+        <v>86449</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9148,38 +9162,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221849</v>
+        <v>6003295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693824</v>
+        <v>693842</v>
       </c>
       <c r="R78" t="n">
-        <v>6360149</v>
+        <v>6360049</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9209,19 +9219,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9236,22 +9236,26 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120389977</v>
+        <v>120382877</v>
       </c>
       <c r="B79" t="n">
-        <v>86417</v>
+        <v>97908</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9260,44 +9264,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6037417</v>
+        <v>219798</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693846</v>
+        <v>694046</v>
       </c>
       <c r="R79" t="n">
-        <v>6360166</v>
+        <v>6360376</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9324,19 +9325,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>10:47</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9351,22 +9342,26 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120390026</v>
+        <v>120382898</v>
       </c>
       <c r="B80" t="n">
-        <v>106872</v>
+        <v>86302</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9375,42 +9370,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220079</v>
+        <v>424</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>693824</v>
+        <v>694010</v>
       </c>
       <c r="R80" t="n">
-        <v>6360149</v>
+        <v>6360337</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9440,19 +9431,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9467,22 +9448,26 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120382897</v>
+        <v>120382862</v>
       </c>
       <c r="B81" t="n">
-        <v>86302</v>
+        <v>86449</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9491,25 +9476,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9519,10 +9504,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693971</v>
+        <v>694014</v>
       </c>
       <c r="R81" t="n">
-        <v>6360459</v>
+        <v>6360294</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9585,10 +9570,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120382146</v>
+        <v>120389965</v>
       </c>
       <c r="B82" t="n">
-        <v>89236</v>
+        <v>86282</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9601,21 +9586,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>245042</v>
+        <v>3712</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9624,17 +9609,17 @@
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Vallagar norra, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693828</v>
+        <v>693783</v>
       </c>
       <c r="R82" t="n">
-        <v>6360094</v>
+        <v>6360146</v>
       </c>
       <c r="S82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9663,7 +9648,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9673,7 +9658,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9688,26 +9673,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120389979</v>
+        <v>120389973</v>
       </c>
       <c r="B83" t="n">
-        <v>86449</v>
+        <v>86373</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9716,25 +9697,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9747,13 +9728,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693831</v>
+        <v>693812</v>
       </c>
       <c r="R83" t="n">
-        <v>6360180</v>
+        <v>6360133</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9782,7 +9763,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9792,7 +9773,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9819,10 +9800,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120382876</v>
+        <v>120390025</v>
       </c>
       <c r="B84" t="n">
-        <v>97908</v>
+        <v>106214</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9831,38 +9812,42 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>221849</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693968</v>
+        <v>693824</v>
       </c>
       <c r="R84" t="n">
-        <v>6360152</v>
+        <v>6360149</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9892,9 +9877,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9909,23 +9904,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120389969</v>
+        <v>120389970</v>
       </c>
       <c r="B85" t="n">
         <v>86302</v>
@@ -9968,10 +9959,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693949</v>
+        <v>693948</v>
       </c>
       <c r="R85" t="n">
-        <v>6360196</v>
+        <v>6360161</v>
       </c>
       <c r="S85" t="n">
         <v>11</v>
@@ -10003,7 +9994,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10013,7 +10004,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10040,7 +10031,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120382891</v>
+        <v>120382893</v>
       </c>
       <c r="B86" t="n">
         <v>89236</v>
@@ -10080,10 +10071,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693948</v>
+        <v>693964</v>
       </c>
       <c r="R86" t="n">
-        <v>6360186</v>
+        <v>6360133</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10146,10 +10137,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120382136</v>
+        <v>120382897</v>
       </c>
       <c r="B87" t="n">
-        <v>86373</v>
+        <v>86302</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10162,40 +10153,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693977</v>
+        <v>693971</v>
       </c>
       <c r="R87" t="n">
-        <v>6360060</v>
+        <v>6360459</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10222,19 +10210,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10249,12 +10227,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10265,10 +10243,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120382888</v>
+        <v>120389967</v>
       </c>
       <c r="B88" t="n">
-        <v>86373</v>
+        <v>86302</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10281,37 +10259,40 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693806</v>
+        <v>693946</v>
       </c>
       <c r="R88" t="n">
-        <v>6359993</v>
+        <v>6360234</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10338,9 +10319,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10355,26 +10346,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120382133</v>
+        <v>120389985</v>
       </c>
       <c r="B89" t="n">
-        <v>86325</v>
+        <v>86465</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10383,25 +10370,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>433</v>
+        <v>248947</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10410,17 +10397,17 @@
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693977</v>
+        <v>693944</v>
       </c>
       <c r="R89" t="n">
-        <v>6360060</v>
+        <v>6360120</v>
       </c>
       <c r="S89" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10449,7 +10436,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10459,7 +10446,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10474,26 +10461,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120390005</v>
+        <v>120393454</v>
       </c>
       <c r="B90" t="n">
-        <v>90028</v>
+        <v>91870</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10506,40 +10489,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4191</v>
+        <v>4366</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>693948</v>
+        <v>694042</v>
       </c>
       <c r="R90" t="n">
-        <v>6360161</v>
+        <v>6360296</v>
       </c>
       <c r="S90" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10566,19 +10546,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:16</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10593,22 +10563,26 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120382900</v>
+        <v>120382135</v>
       </c>
       <c r="B91" t="n">
-        <v>86302</v>
+        <v>86373</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10621,37 +10595,40 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693947</v>
+        <v>693925</v>
       </c>
       <c r="R91" t="n">
-        <v>6360230</v>
+        <v>6360266</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10678,9 +10655,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10695,12 +10682,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10711,10 +10698,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120382145</v>
+        <v>120382149</v>
       </c>
       <c r="B92" t="n">
-        <v>89236</v>
+        <v>90060</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10723,25 +10710,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>245042</v>
+        <v>3286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10750,17 +10737,17 @@
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>694045</v>
+        <v>693887</v>
       </c>
       <c r="R92" t="n">
-        <v>6360164</v>
+        <v>6360046</v>
       </c>
       <c r="S92" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10830,10 +10817,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120382149</v>
+        <v>120401499</v>
       </c>
       <c r="B93" t="n">
-        <v>90060</v>
+        <v>86449</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10846,21 +10833,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10869,17 +10856,17 @@
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>693887</v>
+        <v>694050</v>
       </c>
       <c r="R93" t="n">
-        <v>6360046</v>
+        <v>6360251</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10906,42 +10893,3724 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120393448</v>
+      </c>
+      <c r="B94" t="n">
+        <v>91854</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>694027</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6360257</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120401490</v>
+      </c>
+      <c r="B95" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>694015</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6360329</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>120401494</v>
+      </c>
+      <c r="B96" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>693851</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6360062</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>120382132</v>
+      </c>
+      <c r="B97" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>693977</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6360060</v>
+      </c>
+      <c r="S97" t="n">
+        <v>4</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
           <t>Majken Ekstrand</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
+      <c r="AX97" t="inlineStr">
         <is>
           <t>Majken Ekstrand</t>
         </is>
       </c>
-      <c r="AY93" t="inlineStr">
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>120393470</v>
+      </c>
+      <c r="B98" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>694011</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6360245</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>120393466</v>
+      </c>
+      <c r="B99" t="n">
+        <v>86367</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>449</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>693834</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6360067</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>120401509</v>
+      </c>
+      <c r="B100" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>693873</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6360158</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>120401506</v>
+      </c>
+      <c r="B101" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>693841</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6360091</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>120401498</v>
+      </c>
+      <c r="B102" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>693969</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6360241</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>120401504</v>
+      </c>
+      <c r="B103" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>693797</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6359993</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>120393465</v>
+      </c>
+      <c r="B104" t="n">
+        <v>86367</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>449</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Cortinarius fraudulosus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>694019</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6360356</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>120393464</v>
+      </c>
+      <c r="B105" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>693925</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6360154</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>120393451</v>
+      </c>
+      <c r="B106" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>424</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>694012</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6360247</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>120393452</v>
+      </c>
+      <c r="B107" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>424</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>693937</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6360167</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>120401511</v>
+      </c>
+      <c r="B108" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>424</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>694069</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6360156</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>120401514</v>
+      </c>
+      <c r="B109" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>424</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>693983</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6360175</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>120401496</v>
+      </c>
+      <c r="B110" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>693959</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6360145</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>120393458</v>
+      </c>
+      <c r="B111" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>693861</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6360098</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>120393473</v>
+      </c>
+      <c r="B112" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>693958</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6360192</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>120401510</v>
+      </c>
+      <c r="B113" t="n">
+        <v>86302</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>424</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>693932</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6360232</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>120393468</v>
+      </c>
+      <c r="B114" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>694012</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6360247</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>120401515</v>
+      </c>
+      <c r="B115" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>693926</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6360243</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>120401500</v>
+      </c>
+      <c r="B116" t="n">
+        <v>86414</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>693952</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6360188</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>120401497</v>
+      </c>
+      <c r="B117" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>694026</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6360309</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120401489</v>
+      </c>
+      <c r="B118" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>694061</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6360155</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>120401495</v>
+      </c>
+      <c r="B119" t="n">
+        <v>86222</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Vallhagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>693943</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6360177</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>120393450</v>
+      </c>
+      <c r="B120" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>693928</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6360172</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120393472</v>
+      </c>
+      <c r="B121" t="n">
+        <v>89236</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>693978</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6360202</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120393463</v>
+      </c>
+      <c r="B122" t="n">
+        <v>86373</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>694055</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6360246</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>120393467</v>
+      </c>
+      <c r="B123" t="n">
+        <v>86282</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>693930</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6360168</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>120393449</v>
+      </c>
+      <c r="B124" t="n">
+        <v>90356</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Vit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Hydnum albidum</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>694058</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6360244</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>120393455</v>
+      </c>
+      <c r="B125" t="n">
+        <v>86222</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>694018</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6360242</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>120393456</v>
+      </c>
+      <c r="B126" t="n">
+        <v>86449</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Fröjel, Gtl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>693954</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6360167</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>120382133</v>
+      </c>
+      <c r="B127" t="n">
+        <v>86325</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>433</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>M. M. Moser</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>693977</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6360060</v>
+      </c>
+      <c r="S127" t="n">
+        <v>4</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
         <is>
           <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -5033,10 +5033,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120382145</v>
+        <v>120389969</v>
       </c>
       <c r="B41" t="n">
-        <v>89236</v>
+        <v>86302</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5045,25 +5045,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>245042</v>
+        <v>424</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5072,17 +5072,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>694045</v>
+        <v>693949</v>
       </c>
       <c r="R41" t="n">
-        <v>6360164</v>
+        <v>6360196</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5136,26 +5136,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120382889</v>
+        <v>120382145</v>
       </c>
       <c r="B42" t="n">
-        <v>86367</v>
+        <v>89236</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5164,41 +5160,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>449</v>
+        <v>245042</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>694010</v>
+        <v>694045</v>
       </c>
       <c r="R42" t="n">
-        <v>6360176</v>
+        <v>6360164</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5225,9 +5224,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5242,12 +5251,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5258,10 +5267,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120389969</v>
+        <v>120382889</v>
       </c>
       <c r="B43" t="n">
-        <v>86302</v>
+        <v>86367</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5274,40 +5283,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>424</v>
+        <v>449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>693949</v>
+        <v>694010</v>
       </c>
       <c r="R43" t="n">
-        <v>6360196</v>
+        <v>6360176</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5334,19 +5340,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5361,15 +5357,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6133,10 +6133,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120389981</v>
+        <v>120382131</v>
       </c>
       <c r="B51" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6145,44 +6145,48 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>693941</v>
+        <v>693828</v>
       </c>
       <c r="R51" t="n">
-        <v>6360226</v>
+        <v>6360094</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6211,7 +6215,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6221,7 +6225,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6236,22 +6240,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120382131</v>
+        <v>120389981</v>
       </c>
       <c r="B52" t="n">
-        <v>86282</v>
+        <v>86449</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6260,48 +6268,44 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vallagar norra, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>693828</v>
+        <v>693941</v>
       </c>
       <c r="R52" t="n">
-        <v>6360094</v>
+        <v>6360226</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6330,7 +6334,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6340,7 +6344,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6355,19 +6359,15 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7395,10 +7395,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120389977</v>
+        <v>120382855</v>
       </c>
       <c r="B62" t="n">
-        <v>86417</v>
+        <v>86282</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7407,44 +7407,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6037417</v>
+        <v>3712</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693846</v>
+        <v>694007</v>
       </c>
       <c r="R62" t="n">
-        <v>6360166</v>
+        <v>6360253</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7471,19 +7468,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:47</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7498,22 +7485,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120382855</v>
+        <v>120382876</v>
       </c>
       <c r="B63" t="n">
-        <v>86282</v>
+        <v>97908</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7526,21 +7517,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3712</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7550,10 +7541,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>694007</v>
+        <v>693968</v>
       </c>
       <c r="R63" t="n">
-        <v>6360253</v>
+        <v>6360152</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7616,10 +7607,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120382876</v>
+        <v>120389977</v>
       </c>
       <c r="B64" t="n">
-        <v>97908</v>
+        <v>86417</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7628,41 +7619,44 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219798</v>
+        <v>6037417</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693968</v>
+        <v>693846</v>
       </c>
       <c r="R64" t="n">
-        <v>6360152</v>
+        <v>6360166</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7689,9 +7683,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7706,19 +7710,15 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8143,7 +8143,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120382886</v>
+        <v>120389974</v>
       </c>
       <c r="B69" t="n">
         <v>86373</v>
@@ -8177,19 +8177,22 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>694010</v>
+        <v>693816</v>
       </c>
       <c r="R69" t="n">
-        <v>6360337</v>
+        <v>6360164</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8216,9 +8219,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8233,26 +8246,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120382896</v>
+        <v>120382886</v>
       </c>
       <c r="B70" t="n">
-        <v>86302</v>
+        <v>86373</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8265,21 +8274,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8289,10 +8298,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>694015</v>
+        <v>694010</v>
       </c>
       <c r="R70" t="n">
-        <v>6360173</v>
+        <v>6360337</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8355,10 +8364,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120382150</v>
+        <v>120382896</v>
       </c>
       <c r="B71" t="n">
-        <v>90356</v>
+        <v>86302</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8371,40 +8380,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2015</v>
+        <v>424</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693925</v>
+        <v>694015</v>
       </c>
       <c r="R71" t="n">
-        <v>6360266</v>
+        <v>6360173</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8431,19 +8437,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8458,12 +8454,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8474,10 +8470,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120389974</v>
+        <v>120382150</v>
       </c>
       <c r="B72" t="n">
-        <v>86373</v>
+        <v>90356</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8490,21 +8486,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8513,17 +8509,17 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>693816</v>
+        <v>693925</v>
       </c>
       <c r="R72" t="n">
-        <v>6360164</v>
+        <v>6360266</v>
       </c>
       <c r="S72" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8552,7 +8548,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8562,7 +8558,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8577,22 +8573,26 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120389966</v>
+        <v>120389982</v>
       </c>
       <c r="B73" t="n">
-        <v>86282</v>
+        <v>86449</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8601,25 +8601,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693948</v>
+        <v>693945</v>
       </c>
       <c r="R73" t="n">
-        <v>6360161</v>
+        <v>6360147</v>
       </c>
       <c r="S73" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8704,10 +8704,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120389982</v>
+        <v>120389966</v>
       </c>
       <c r="B74" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8716,25 +8716,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8747,13 +8747,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>693945</v>
+        <v>693948</v>
       </c>
       <c r="R74" t="n">
-        <v>6360147</v>
+        <v>6360161</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10579,10 +10579,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120382135</v>
+        <v>120382149</v>
       </c>
       <c r="B91" t="n">
-        <v>86373</v>
+        <v>90060</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10591,25 +10591,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>248956</v>
+        <v>3286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10618,17 +10618,17 @@
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693925</v>
+        <v>693887</v>
       </c>
       <c r="R91" t="n">
-        <v>6360266</v>
+        <v>6360046</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10698,10 +10698,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120382149</v>
+        <v>120382135</v>
       </c>
       <c r="B92" t="n">
-        <v>90060</v>
+        <v>86373</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10710,25 +10710,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3286</v>
+        <v>248956</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10737,17 +10737,17 @@
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Vallagar norra (Vallhagar norra), Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693887</v>
+        <v>693925</v>
       </c>
       <c r="R92" t="n">
-        <v>6360046</v>
+        <v>6360266</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -4034,10 +4034,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120382142</v>
+        <v>120382858</v>
       </c>
       <c r="B32" t="n">
-        <v>86414</v>
+        <v>91872</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4050,40 +4050,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3674</v>
+        <v>6047725</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693925</v>
+        <v>694046</v>
       </c>
       <c r="R32" t="n">
-        <v>6360266</v>
+        <v>6360382</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,39 +4103,30 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4153,7 +4137,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120382856</v>
+        <v>120382855</v>
       </c>
       <c r="B33" t="n">
         <v>86282</v>
@@ -4193,10 +4177,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>693985</v>
+        <v>694007</v>
       </c>
       <c r="R33" t="n">
-        <v>6360386</v>
+        <v>6360253</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4259,7 +4243,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120382899</v>
+        <v>120389970</v>
       </c>
       <c r="B34" t="n">
         <v>86302</v>
@@ -4293,19 +4277,22 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>694017</v>
+        <v>693948</v>
       </c>
       <c r="R34" t="n">
-        <v>6360293</v>
+        <v>6360161</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4332,9 +4319,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4349,26 +4346,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120382861</v>
+        <v>120382897</v>
       </c>
       <c r="B35" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4377,25 +4370,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4405,10 +4398,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>694007</v>
+        <v>693971</v>
       </c>
       <c r="R35" t="n">
-        <v>6360345</v>
+        <v>6360459</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4471,10 +4464,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120390026</v>
+        <v>120389982</v>
       </c>
       <c r="B36" t="n">
-        <v>106872</v>
+        <v>86449</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4487,41 +4480,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>693824</v>
+        <v>693945</v>
       </c>
       <c r="R36" t="n">
-        <v>6360149</v>
+        <v>6360147</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4550,7 +4542,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4560,7 +4552,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4587,10 +4579,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120389980</v>
+        <v>120382857</v>
       </c>
       <c r="B37" t="n">
-        <v>86449</v>
+        <v>90351</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4599,44 +4591,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6003295</v>
+        <v>3215</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>693909</v>
+        <v>693914</v>
       </c>
       <c r="R37" t="n">
-        <v>6360231</v>
+        <v>6360179</v>
       </c>
       <c r="S37" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4663,19 +4652,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4690,22 +4669,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120382881</v>
+        <v>120382900</v>
       </c>
       <c r="B38" t="n">
-        <v>85676</v>
+        <v>86302</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4714,25 +4697,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4852</v>
+        <v>424</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kastanjefjällskivling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lepiota castanea</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4742,10 +4725,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>693945</v>
+        <v>693947</v>
       </c>
       <c r="R38" t="n">
-        <v>6360205</v>
+        <v>6360230</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4808,10 +4791,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120382146</v>
+        <v>120389973</v>
       </c>
       <c r="B39" t="n">
-        <v>89236</v>
+        <v>86373</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4820,25 +4803,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>245042</v>
+        <v>248956</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4847,17 +4830,17 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vallagar norra, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>693828</v>
+        <v>693812</v>
       </c>
       <c r="R39" t="n">
-        <v>6360094</v>
+        <v>6360133</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4896,7 +4879,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4911,26 +4894,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120382895</v>
+        <v>120389980</v>
       </c>
       <c r="B40" t="n">
-        <v>89236</v>
+        <v>86449</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4939,41 +4918,44 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>245042</v>
+        <v>6003295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>693867</v>
+        <v>693909</v>
       </c>
       <c r="R40" t="n">
-        <v>6360109</v>
+        <v>6360231</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5000,9 +4982,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5017,26 +5009,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120389969</v>
+        <v>120382856</v>
       </c>
       <c r="B41" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5045,44 +5033,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>693949</v>
+        <v>693985</v>
       </c>
       <c r="R41" t="n">
-        <v>6360196</v>
+        <v>6360386</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5109,19 +5094,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5136,15 +5111,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5267,10 +5246,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120382889</v>
+        <v>120389985</v>
       </c>
       <c r="B43" t="n">
-        <v>86367</v>
+        <v>86465</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5279,41 +5258,44 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>449</v>
+        <v>248947</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>694010</v>
+        <v>693944</v>
       </c>
       <c r="R43" t="n">
-        <v>6360176</v>
+        <v>6360120</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5340,9 +5322,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5357,26 +5349,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120382854</v>
+        <v>120382136</v>
       </c>
       <c r="B44" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5385,41 +5373,44 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>694079</v>
+        <v>693977</v>
       </c>
       <c r="R44" t="n">
-        <v>6360242</v>
+        <v>6360060</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5446,9 +5437,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5463,12 +5464,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5479,10 +5480,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120382900</v>
+        <v>120382146</v>
       </c>
       <c r="B45" t="n">
-        <v>86302</v>
+        <v>89236</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5491,41 +5492,44 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>424</v>
+        <v>245042</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>693947</v>
+        <v>693828</v>
       </c>
       <c r="R45" t="n">
-        <v>6360230</v>
+        <v>6360094</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5552,9 +5556,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5569,12 +5583,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5585,10 +5599,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120382901</v>
+        <v>120389981</v>
       </c>
       <c r="B46" t="n">
-        <v>86414</v>
+        <v>86449</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5597,41 +5611,44 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>693951</v>
+        <v>693941</v>
       </c>
       <c r="R46" t="n">
-        <v>6360191</v>
+        <v>6360226</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5658,9 +5675,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5675,26 +5702,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120390006</v>
+        <v>120382143</v>
       </c>
       <c r="B47" t="n">
-        <v>90356</v>
+        <v>86449</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5703,25 +5726,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5730,17 +5753,17 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>693959</v>
+        <v>693925</v>
       </c>
       <c r="R47" t="n">
-        <v>6360193</v>
+        <v>6360266</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5769,7 +5792,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5779,7 +5802,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5794,22 +5817,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120389972</v>
+        <v>120382148</v>
       </c>
       <c r="B48" t="n">
-        <v>86325</v>
+        <v>90021</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5818,25 +5845,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>433</v>
+        <v>4188</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5845,17 +5872,17 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>693952</v>
+        <v>693828</v>
       </c>
       <c r="R48" t="n">
-        <v>6360138</v>
+        <v>6360094</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5884,7 +5911,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5894,7 +5921,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5909,22 +5936,26 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120382847</v>
+        <v>120382876</v>
       </c>
       <c r="B49" t="n">
-        <v>90356</v>
+        <v>97908</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5933,25 +5964,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2015</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5961,10 +5992,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693960</v>
+        <v>693968</v>
       </c>
       <c r="R49" t="n">
-        <v>6360226</v>
+        <v>6360152</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6027,10 +6058,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120382891</v>
+        <v>120382859</v>
       </c>
       <c r="B50" t="n">
-        <v>89236</v>
+        <v>86222</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6043,21 +6074,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>245042</v>
+        <v>3762</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6067,10 +6098,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>693948</v>
+        <v>693938</v>
       </c>
       <c r="R50" t="n">
-        <v>6360186</v>
+        <v>6360238</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6133,10 +6164,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120382131</v>
+        <v>120382877</v>
       </c>
       <c r="B51" t="n">
-        <v>86282</v>
+        <v>97908</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6149,44 +6180,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3712</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Vallagar norra, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>693828</v>
+        <v>694046</v>
       </c>
       <c r="R51" t="n">
-        <v>6360094</v>
+        <v>6360376</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6213,19 +6237,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6240,12 +6254,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6256,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120389981</v>
+        <v>120382896</v>
       </c>
       <c r="B52" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6268,44 +6282,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>693941</v>
+        <v>694015</v>
       </c>
       <c r="R52" t="n">
-        <v>6360226</v>
+        <v>6360173</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6332,19 +6343,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6359,22 +6360,26 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120382143</v>
+        <v>120382131</v>
       </c>
       <c r="B53" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6383,41 +6388,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693925</v>
+        <v>693828</v>
       </c>
       <c r="R53" t="n">
-        <v>6360266</v>
+        <v>6360094</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6490,10 +6499,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120382857</v>
+        <v>120382895</v>
       </c>
       <c r="B54" t="n">
-        <v>90351</v>
+        <v>89236</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6506,21 +6515,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3215</v>
+        <v>245042</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6530,10 +6539,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693914</v>
+        <v>693867</v>
       </c>
       <c r="R54" t="n">
-        <v>6360179</v>
+        <v>6360109</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6596,10 +6605,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120382147</v>
+        <v>120382142</v>
       </c>
       <c r="B55" t="n">
-        <v>90021</v>
+        <v>86414</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6612,21 +6621,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4188</v>
+        <v>3674</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6715,10 +6724,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120390004</v>
+        <v>120382848</v>
       </c>
       <c r="B56" t="n">
-        <v>90021</v>
+        <v>90356</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6727,44 +6736,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4188</v>
+        <v>2015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>693783</v>
+        <v>693804</v>
       </c>
       <c r="R56" t="n">
-        <v>6360146</v>
+        <v>6360012</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6791,19 +6797,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>10:41</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>10:41</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6818,22 +6814,26 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120382888</v>
+        <v>120382889</v>
       </c>
       <c r="B57" t="n">
-        <v>86373</v>
+        <v>86367</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693806</v>
+        <v>694010</v>
       </c>
       <c r="R57" t="n">
-        <v>6359993</v>
+        <v>6360176</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6936,10 +6936,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120382148</v>
+        <v>120389965</v>
       </c>
       <c r="B58" t="n">
-        <v>90021</v>
+        <v>86282</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6952,21 +6952,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4188</v>
+        <v>3712</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6975,17 +6975,17 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vallagar norra, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693828</v>
+        <v>693783</v>
       </c>
       <c r="R58" t="n">
-        <v>6360094</v>
+        <v>6360146</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7039,26 +7039,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120382864</v>
+        <v>120382845</v>
       </c>
       <c r="B59" t="n">
-        <v>86449</v>
+        <v>90356</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7067,25 +7063,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7095,10 +7091,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>693969</v>
+        <v>694018</v>
       </c>
       <c r="R59" t="n">
-        <v>6360153</v>
+        <v>6360293</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7161,10 +7157,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120382136</v>
+        <v>120382894</v>
       </c>
       <c r="B60" t="n">
-        <v>86373</v>
+        <v>89236</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7173,44 +7169,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>693977</v>
+        <v>694014</v>
       </c>
       <c r="R60" t="n">
-        <v>6360060</v>
+        <v>6360338</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7237,19 +7230,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7264,12 +7247,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7280,10 +7263,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120390005</v>
+        <v>120389977</v>
       </c>
       <c r="B61" t="n">
-        <v>90028</v>
+        <v>86417</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7292,25 +7275,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4191</v>
+        <v>6037417</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7319,17 +7302,17 @@
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693948</v>
+        <v>693846</v>
       </c>
       <c r="R61" t="n">
-        <v>6360161</v>
+        <v>6360166</v>
       </c>
       <c r="S61" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7358,7 +7341,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7368,7 +7351,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7395,10 +7378,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120382855</v>
+        <v>120389972</v>
       </c>
       <c r="B62" t="n">
-        <v>86282</v>
+        <v>86325</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7407,38 +7390,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3712</v>
+        <v>433</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius caesiocanescens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>694007</v>
+        <v>693952</v>
       </c>
       <c r="R62" t="n">
-        <v>6360253</v>
+        <v>6360138</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7468,9 +7454,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7485,26 +7481,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120382876</v>
+        <v>120382898</v>
       </c>
       <c r="B63" t="n">
-        <v>97908</v>
+        <v>86302</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7513,25 +7505,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219798</v>
+        <v>424</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7541,10 +7533,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>693968</v>
+        <v>694010</v>
       </c>
       <c r="R63" t="n">
-        <v>6360152</v>
+        <v>6360337</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7607,10 +7599,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120389977</v>
+        <v>120390005</v>
       </c>
       <c r="B64" t="n">
-        <v>86417</v>
+        <v>90028</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7619,25 +7611,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6037417</v>
+        <v>4191</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7646,17 +7638,17 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693846</v>
+        <v>693948</v>
       </c>
       <c r="R64" t="n">
-        <v>6360166</v>
+        <v>6360161</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7685,7 +7677,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7695,7 +7687,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7722,10 +7714,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120382848</v>
+        <v>120382901</v>
       </c>
       <c r="B65" t="n">
-        <v>90356</v>
+        <v>86414</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7734,25 +7726,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2015</v>
+        <v>3674</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7762,10 +7754,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693804</v>
+        <v>693951</v>
       </c>
       <c r="R65" t="n">
-        <v>6360012</v>
+        <v>6360191</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7828,10 +7820,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120382858</v>
+        <v>120390004</v>
       </c>
       <c r="B66" t="n">
-        <v>91872</v>
+        <v>90021</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7844,33 +7836,40 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6047725</v>
+        <v>4188</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Geastrum fimbriatum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>694046</v>
+        <v>693783</v>
       </c>
       <c r="R66" t="n">
-        <v>6360382</v>
+        <v>6360146</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7897,44 +7896,49 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120382853</v>
+        <v>120382864</v>
       </c>
       <c r="B67" t="n">
-        <v>57336</v>
+        <v>86449</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7947,21 +7951,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6003295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7971,10 +7975,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>693992</v>
+        <v>693969</v>
       </c>
       <c r="R67" t="n">
-        <v>6360385</v>
+        <v>6360153</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8037,10 +8041,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120382859</v>
+        <v>120382886</v>
       </c>
       <c r="B68" t="n">
-        <v>86222</v>
+        <v>86373</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8049,25 +8053,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8077,10 +8081,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>693938</v>
+        <v>694010</v>
       </c>
       <c r="R68" t="n">
-        <v>6360238</v>
+        <v>6360337</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8143,10 +8147,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120389974</v>
+        <v>120382899</v>
       </c>
       <c r="B69" t="n">
-        <v>86373</v>
+        <v>86302</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8159,40 +8163,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>693816</v>
+        <v>694017</v>
       </c>
       <c r="R69" t="n">
-        <v>6360164</v>
+        <v>6360293</v>
       </c>
       <c r="S69" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8219,19 +8220,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8246,22 +8237,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120382886</v>
+        <v>120382847</v>
       </c>
       <c r="B70" t="n">
-        <v>86373</v>
+        <v>90356</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8274,21 +8269,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8298,10 +8293,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>694010</v>
+        <v>693960</v>
       </c>
       <c r="R70" t="n">
-        <v>6360337</v>
+        <v>6360226</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8364,10 +8359,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120382896</v>
+        <v>120382888</v>
       </c>
       <c r="B71" t="n">
-        <v>86302</v>
+        <v>86373</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8380,21 +8375,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8404,10 +8399,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>694015</v>
+        <v>693806</v>
       </c>
       <c r="R71" t="n">
-        <v>6360173</v>
+        <v>6359993</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8589,7 +8584,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120389982</v>
+        <v>120389979</v>
       </c>
       <c r="B73" t="n">
         <v>86449</v>
@@ -8628,17 +8623,17 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693945</v>
+        <v>693831</v>
       </c>
       <c r="R73" t="n">
-        <v>6360147</v>
+        <v>6360180</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8667,7 +8662,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8677,7 +8672,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8704,10 +8699,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120389966</v>
+        <v>120382861</v>
       </c>
       <c r="B74" t="n">
-        <v>86282</v>
+        <v>86449</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8716,44 +8711,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>693948</v>
+        <v>694007</v>
       </c>
       <c r="R74" t="n">
-        <v>6360161</v>
+        <v>6360345</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8780,19 +8772,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>11:16</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8807,22 +8789,26 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120389979</v>
+        <v>120382854</v>
       </c>
       <c r="B75" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8831,44 +8817,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>693831</v>
+        <v>694079</v>
       </c>
       <c r="R75" t="n">
-        <v>6360180</v>
+        <v>6360242</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8895,19 +8878,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8922,19 +8895,23 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120382845</v>
+        <v>120390006</v>
       </c>
       <c r="B76" t="n">
         <v>90356</v>
@@ -8968,19 +8945,22 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>694018</v>
+        <v>693959</v>
       </c>
       <c r="R76" t="n">
-        <v>6360293</v>
+        <v>6360193</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9007,9 +8987,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9024,23 +9014,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120382894</v>
+        <v>120382891</v>
       </c>
       <c r="B77" t="n">
         <v>89236</v>
@@ -9080,10 +9066,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>694014</v>
+        <v>693948</v>
       </c>
       <c r="R77" t="n">
-        <v>6360338</v>
+        <v>6360186</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9146,10 +9132,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120382863</v>
+        <v>120389974</v>
       </c>
       <c r="B78" t="n">
-        <v>86449</v>
+        <v>86373</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9158,41 +9144,44 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693842</v>
+        <v>693816</v>
       </c>
       <c r="R78" t="n">
-        <v>6360049</v>
+        <v>6360164</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9219,9 +9208,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9236,26 +9235,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120382877</v>
+        <v>120382863</v>
       </c>
       <c r="B79" t="n">
-        <v>97908</v>
+        <v>86449</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9264,25 +9259,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219798</v>
+        <v>6003295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9292,10 +9287,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>694046</v>
+        <v>693842</v>
       </c>
       <c r="R79" t="n">
-        <v>6360376</v>
+        <v>6360049</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9358,7 +9353,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120382898</v>
+        <v>120389969</v>
       </c>
       <c r="B80" t="n">
         <v>86302</v>
@@ -9392,19 +9387,22 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>694010</v>
+        <v>693949</v>
       </c>
       <c r="R80" t="n">
-        <v>6360337</v>
+        <v>6360196</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9431,9 +9429,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9448,26 +9456,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120382862</v>
+        <v>120382853</v>
       </c>
       <c r="B81" t="n">
-        <v>86449</v>
+        <v>57336</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9480,21 +9484,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9504,10 +9508,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>694014</v>
+        <v>693992</v>
       </c>
       <c r="R81" t="n">
-        <v>6360294</v>
+        <v>6360385</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9570,7 +9574,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120389965</v>
+        <v>120389966</v>
       </c>
       <c r="B82" t="n">
         <v>86282</v>
@@ -9609,17 +9613,17 @@
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>693783</v>
+        <v>693948</v>
       </c>
       <c r="R82" t="n">
-        <v>6360146</v>
+        <v>6360161</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9648,7 +9652,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9658,7 +9662,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9685,10 +9689,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120389973</v>
+        <v>120382881</v>
       </c>
       <c r="B83" t="n">
-        <v>86373</v>
+        <v>85676</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9697,44 +9701,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>248956</v>
+        <v>4852</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Kastanjefjällskivling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lepiota castanea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>693812</v>
+        <v>693945</v>
       </c>
       <c r="R83" t="n">
-        <v>6360133</v>
+        <v>6360205</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9761,19 +9762,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9788,22 +9779,26 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120390025</v>
+        <v>120382147</v>
       </c>
       <c r="B84" t="n">
-        <v>106214</v>
+        <v>90021</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9812,45 +9807,44 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221849</v>
+        <v>4188</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Vallagar norra, Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693824</v>
+        <v>693925</v>
       </c>
       <c r="R84" t="n">
-        <v>6360149</v>
+        <v>6360266</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9879,7 +9873,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9889,7 +9883,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9904,19 +9898,23 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Majken Ekstrand</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120389970</v>
+        <v>120389967</v>
       </c>
       <c r="B85" t="n">
         <v>86302</v>
@@ -9959,13 +9957,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>693948</v>
+        <v>693946</v>
       </c>
       <c r="R85" t="n">
-        <v>6360161</v>
+        <v>6360234</v>
       </c>
       <c r="S85" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9994,7 +9992,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10004,7 +10002,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10031,10 +10029,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120382893</v>
+        <v>120390025</v>
       </c>
       <c r="B86" t="n">
-        <v>89236</v>
+        <v>106214</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10043,38 +10041,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>245042</v>
+        <v>221849</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>693964</v>
+        <v>693824</v>
       </c>
       <c r="R86" t="n">
-        <v>6360133</v>
+        <v>6360149</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10104,9 +10106,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10121,26 +10133,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120382897</v>
+        <v>120390026</v>
       </c>
       <c r="B87" t="n">
-        <v>86302</v>
+        <v>106872</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10149,38 +10157,42 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>424</v>
+        <v>220079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693971</v>
+        <v>693824</v>
       </c>
       <c r="R87" t="n">
-        <v>6360459</v>
+        <v>6360149</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10210,9 +10222,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10227,26 +10249,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120389967</v>
+        <v>120382893</v>
       </c>
       <c r="B88" t="n">
-        <v>86302</v>
+        <v>89236</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10255,44 +10273,41 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>424</v>
+        <v>245042</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693946</v>
+        <v>693964</v>
       </c>
       <c r="R88" t="n">
-        <v>6360234</v>
+        <v>6360133</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10319,19 +10334,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10346,22 +10351,26 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120389985</v>
+        <v>120382862</v>
       </c>
       <c r="B89" t="n">
-        <v>86465</v>
+        <v>86449</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10370,44 +10379,41 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693944</v>
+        <v>694014</v>
       </c>
       <c r="R89" t="n">
-        <v>6360120</v>
+        <v>6360294</v>
       </c>
       <c r="S89" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10434,19 +10440,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10461,22 +10457,26 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120393454</v>
+        <v>120401514</v>
       </c>
       <c r="B90" t="n">
-        <v>91870</v>
+        <v>86302</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10485,38 +10485,41 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4366</v>
+        <v>424</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>694042</v>
+        <v>693983</v>
       </c>
       <c r="R90" t="n">
-        <v>6360296</v>
+        <v>6360175</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10557,18 +10560,19 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10579,10 +10583,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120382149</v>
+        <v>120401498</v>
       </c>
       <c r="B91" t="n">
-        <v>90060</v>
+        <v>86449</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10595,21 +10599,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3286</v>
+        <v>6003295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10618,17 +10622,17 @@
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Vallagar norra (Vallhagar norra), Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693887</v>
+        <v>693969</v>
       </c>
       <c r="R91" t="n">
-        <v>6360046</v>
+        <v>6360241</v>
       </c>
       <c r="S91" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10655,39 +10659,30 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10698,10 +10693,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120382135</v>
+        <v>120393450</v>
       </c>
       <c r="B92" t="n">
-        <v>86373</v>
+        <v>90356</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10714,40 +10709,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693925</v>
+        <v>693928</v>
       </c>
       <c r="R92" t="n">
-        <v>6360266</v>
+        <v>6360172</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10774,19 +10766,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10801,12 +10783,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -10817,10 +10799,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120401499</v>
+        <v>120393467</v>
       </c>
       <c r="B93" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10829,41 +10811,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>694050</v>
+        <v>693930</v>
       </c>
       <c r="R93" t="n">
-        <v>6360251</v>
+        <v>6360168</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10904,19 +10883,18 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10927,10 +10905,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120393448</v>
+        <v>120393473</v>
       </c>
       <c r="B94" t="n">
-        <v>91854</v>
+        <v>89236</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10943,21 +10921,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4363</v>
+        <v>245042</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10967,10 +10945,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>694027</v>
+        <v>693958</v>
       </c>
       <c r="R94" t="n">
-        <v>6360257</v>
+        <v>6360192</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11033,10 +11011,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120401490</v>
+        <v>120393466</v>
       </c>
       <c r="B95" t="n">
-        <v>90356</v>
+        <v>86367</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11049,37 +11027,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2015</v>
+        <v>449</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>694015</v>
+        <v>693834</v>
       </c>
       <c r="R95" t="n">
-        <v>6360329</v>
+        <v>6360067</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11120,19 +11095,18 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11143,10 +11117,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120401494</v>
+        <v>120393456</v>
       </c>
       <c r="B96" t="n">
-        <v>86282</v>
+        <v>86449</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11155,41 +11129,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>693851</v>
+        <v>693954</v>
       </c>
       <c r="R96" t="n">
-        <v>6360062</v>
+        <v>6360167</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11230,19 +11201,18 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11253,10 +11223,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120382132</v>
+        <v>120401489</v>
       </c>
       <c r="B97" t="n">
-        <v>86282</v>
+        <v>90356</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11265,25 +11235,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3712</v>
+        <v>2015</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11292,17 +11262,17 @@
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>693977</v>
+        <v>694061</v>
       </c>
       <c r="R97" t="n">
-        <v>6360060</v>
+        <v>6360155</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11329,39 +11299,30 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11478,10 +11439,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120393466</v>
+        <v>120401504</v>
       </c>
       <c r="B99" t="n">
-        <v>86367</v>
+        <v>86373</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11494,34 +11455,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>693834</v>
+        <v>693797</v>
       </c>
       <c r="R99" t="n">
-        <v>6360067</v>
+        <v>6359993</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11562,18 +11526,19 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11584,10 +11549,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120401509</v>
+        <v>120401511</v>
       </c>
       <c r="B100" t="n">
-        <v>89236</v>
+        <v>86302</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11596,25 +11561,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>245042</v>
+        <v>424</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11627,10 +11592,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>693873</v>
+        <v>694069</v>
       </c>
       <c r="R100" t="n">
-        <v>6360158</v>
+        <v>6360156</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11694,10 +11659,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120401506</v>
+        <v>120393449</v>
       </c>
       <c r="B101" t="n">
-        <v>86373</v>
+        <v>90356</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11710,37 +11675,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>693841</v>
+        <v>694058</v>
       </c>
       <c r="R101" t="n">
-        <v>6360091</v>
+        <v>6360244</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11781,19 +11743,18 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11804,10 +11765,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120401498</v>
+        <v>120393465</v>
       </c>
       <c r="B102" t="n">
-        <v>86449</v>
+        <v>86367</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11816,41 +11777,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693969</v>
+        <v>694019</v>
       </c>
       <c r="R102" t="n">
-        <v>6360241</v>
+        <v>6360356</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11891,19 +11849,18 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11914,10 +11871,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120401504</v>
+        <v>120401500</v>
       </c>
       <c r="B103" t="n">
-        <v>86373</v>
+        <v>86414</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11926,25 +11883,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>248956</v>
+        <v>3674</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11957,10 +11914,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693797</v>
+        <v>693952</v>
       </c>
       <c r="R103" t="n">
-        <v>6359993</v>
+        <v>6360188</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12024,10 +11981,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120393465</v>
+        <v>120401506</v>
       </c>
       <c r="B104" t="n">
-        <v>86367</v>
+        <v>86373</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12040,34 +11997,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>694019</v>
+        <v>693841</v>
       </c>
       <c r="R104" t="n">
-        <v>6360356</v>
+        <v>6360091</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12108,18 +12068,19 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12130,7 +12091,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120393464</v>
+        <v>120382135</v>
       </c>
       <c r="B105" t="n">
         <v>86373</v>
@@ -12164,19 +12125,22 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
         <v>693925</v>
       </c>
       <c r="R105" t="n">
-        <v>6360154</v>
+        <v>6360266</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12203,9 +12167,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12220,12 +12194,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -12236,10 +12210,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120393451</v>
+        <v>120393468</v>
       </c>
       <c r="B106" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12248,25 +12222,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12320,6 +12294,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -12342,10 +12317,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120393452</v>
+        <v>120401490</v>
       </c>
       <c r="B107" t="n">
-        <v>86302</v>
+        <v>90356</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12358,34 +12333,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>693937</v>
+        <v>694015</v>
       </c>
       <c r="R107" t="n">
-        <v>6360167</v>
+        <v>6360329</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12426,18 +12404,19 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -12448,10 +12427,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120401511</v>
+        <v>120382133</v>
       </c>
       <c r="B108" t="n">
-        <v>86302</v>
+        <v>86325</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12464,21 +12443,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius caesiocanescens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12487,17 +12466,17 @@
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>694069</v>
+        <v>693977</v>
       </c>
       <c r="R108" t="n">
-        <v>6360156</v>
+        <v>6360060</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12524,30 +12503,39 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12558,10 +12546,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120401514</v>
+        <v>120393454</v>
       </c>
       <c r="B109" t="n">
-        <v>86302</v>
+        <v>91870</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12570,41 +12558,38 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>424</v>
+        <v>4366</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>693983</v>
+        <v>694042</v>
       </c>
       <c r="R109" t="n">
-        <v>6360175</v>
+        <v>6360296</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12645,19 +12630,18 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12668,10 +12652,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120401496</v>
+        <v>120401494</v>
       </c>
       <c r="B110" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12680,25 +12664,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12711,10 +12695,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>693959</v>
+        <v>693851</v>
       </c>
       <c r="R110" t="n">
-        <v>6360145</v>
+        <v>6360062</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12778,10 +12762,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120393458</v>
+        <v>120382132</v>
       </c>
       <c r="B111" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12790,41 +12774,44 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>693861</v>
+        <v>693977</v>
       </c>
       <c r="R111" t="n">
-        <v>6360098</v>
+        <v>6360060</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12851,9 +12838,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12868,12 +12865,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12884,7 +12881,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120393473</v>
+        <v>120401509</v>
       </c>
       <c r="B112" t="n">
         <v>89236</v>
@@ -12918,16 +12915,19 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>693958</v>
+        <v>693873</v>
       </c>
       <c r="R112" t="n">
-        <v>6360192</v>
+        <v>6360158</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12968,18 +12968,19 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12990,7 +12991,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120401510</v>
+        <v>120393451</v>
       </c>
       <c r="B113" t="n">
         <v>86302</v>
@@ -13024,19 +13025,16 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>693932</v>
+        <v>694012</v>
       </c>
       <c r="R113" t="n">
-        <v>6360232</v>
+        <v>6360247</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13077,19 +13075,18 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13100,10 +13097,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120393468</v>
+        <v>120393455</v>
       </c>
       <c r="B114" t="n">
-        <v>86282</v>
+        <v>86222</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13116,21 +13113,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13140,10 +13137,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>694012</v>
+        <v>694018</v>
       </c>
       <c r="R114" t="n">
-        <v>6360247</v>
+        <v>6360242</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13184,7 +13181,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -13207,10 +13203,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120401515</v>
+        <v>120382149</v>
       </c>
       <c r="B115" t="n">
-        <v>86414</v>
+        <v>90060</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13219,25 +13215,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3674</v>
+        <v>3286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13246,17 +13242,17 @@
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>693926</v>
+        <v>693887</v>
       </c>
       <c r="R115" t="n">
-        <v>6360243</v>
+        <v>6360046</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13283,30 +13279,39 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -13317,10 +13322,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120401500</v>
+        <v>120393458</v>
       </c>
       <c r="B116" t="n">
-        <v>86414</v>
+        <v>86449</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13329,41 +13334,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>693952</v>
+        <v>693861</v>
       </c>
       <c r="R116" t="n">
-        <v>6360188</v>
+        <v>6360098</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13404,19 +13406,18 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -13427,10 +13428,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120401497</v>
+        <v>120393452</v>
       </c>
       <c r="B117" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13439,41 +13440,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>694026</v>
+        <v>693937</v>
       </c>
       <c r="R117" t="n">
-        <v>6360309</v>
+        <v>6360167</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13514,19 +13512,18 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -13537,10 +13534,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120401489</v>
+        <v>120401515</v>
       </c>
       <c r="B118" t="n">
-        <v>90356</v>
+        <v>86414</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13549,25 +13546,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2015</v>
+        <v>3674</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13580,10 +13577,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>694061</v>
+        <v>693926</v>
       </c>
       <c r="R118" t="n">
-        <v>6360155</v>
+        <v>6360243</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13647,10 +13644,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120401495</v>
+        <v>120393472</v>
       </c>
       <c r="B119" t="n">
-        <v>86222</v>
+        <v>89236</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13663,37 +13660,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3762</v>
+        <v>245042</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>693943</v>
+        <v>693978</v>
       </c>
       <c r="R119" t="n">
-        <v>6360177</v>
+        <v>6360202</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13734,19 +13728,18 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -13757,10 +13750,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120393450</v>
+        <v>120401499</v>
       </c>
       <c r="B120" t="n">
-        <v>90356</v>
+        <v>86449</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13769,38 +13762,41 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>693928</v>
+        <v>694050</v>
       </c>
       <c r="R120" t="n">
-        <v>6360172</v>
+        <v>6360251</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13841,18 +13837,19 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13863,10 +13860,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120393472</v>
+        <v>120401510</v>
       </c>
       <c r="B121" t="n">
-        <v>89236</v>
+        <v>86302</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13875,38 +13872,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>245042</v>
+        <v>424</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>693978</v>
+        <v>693932</v>
       </c>
       <c r="R121" t="n">
-        <v>6360202</v>
+        <v>6360232</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13947,18 +13947,19 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -13969,10 +13970,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120393463</v>
+        <v>120393448</v>
       </c>
       <c r="B122" t="n">
-        <v>86373</v>
+        <v>91854</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13981,25 +13982,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>248956</v>
+        <v>4363</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14009,10 +14010,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>694055</v>
+        <v>694027</v>
       </c>
       <c r="R122" t="n">
-        <v>6360246</v>
+        <v>6360257</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14075,10 +14076,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120393467</v>
+        <v>120393464</v>
       </c>
       <c r="B123" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14087,25 +14088,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14115,10 +14116,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>693930</v>
+        <v>693925</v>
       </c>
       <c r="R123" t="n">
-        <v>6360168</v>
+        <v>6360154</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14181,10 +14182,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120393449</v>
+        <v>120393463</v>
       </c>
       <c r="B124" t="n">
-        <v>90356</v>
+        <v>86373</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14197,21 +14198,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14221,10 +14222,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>694058</v>
+        <v>694055</v>
       </c>
       <c r="R124" t="n">
-        <v>6360244</v>
+        <v>6360246</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14287,10 +14288,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120393455</v>
+        <v>120401497</v>
       </c>
       <c r="B125" t="n">
-        <v>86222</v>
+        <v>86449</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14299,38 +14300,41 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3762</v>
+        <v>6003295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>694018</v>
+        <v>694026</v>
       </c>
       <c r="R125" t="n">
-        <v>6360242</v>
+        <v>6360309</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14371,18 +14375,19 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -14393,10 +14398,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120393456</v>
+        <v>120401495</v>
       </c>
       <c r="B126" t="n">
-        <v>86449</v>
+        <v>86222</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14405,38 +14410,41 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>693954</v>
+        <v>693943</v>
       </c>
       <c r="R126" t="n">
-        <v>6360167</v>
+        <v>6360177</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14477,18 +14485,19 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -14499,10 +14508,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120382133</v>
+        <v>120401496</v>
       </c>
       <c r="B127" t="n">
-        <v>86325</v>
+        <v>86449</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14511,25 +14520,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>433</v>
+        <v>6003295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14538,17 +14547,17 @@
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Vallagar norra, Vallagar norra, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>693977</v>
+        <v>693959</v>
       </c>
       <c r="R127" t="n">
-        <v>6360060</v>
+        <v>6360145</v>
       </c>
       <c r="S127" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14575,39 +14584,30 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -6270,10 +6270,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120382896</v>
+        <v>120382131</v>
       </c>
       <c r="B52" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6282,41 +6282,48 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>694015</v>
+        <v>693828</v>
       </c>
       <c r="R52" t="n">
-        <v>6360173</v>
+        <v>6360094</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6343,9 +6350,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6360,12 +6377,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6376,10 +6393,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120382131</v>
+        <v>120382896</v>
       </c>
       <c r="B53" t="n">
-        <v>86282</v>
+        <v>86302</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6388,48 +6405,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Vallagar norra, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693828</v>
+        <v>694015</v>
       </c>
       <c r="R53" t="n">
-        <v>6360094</v>
+        <v>6360173</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6456,19 +6466,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6483,12 +6483,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -7263,10 +7263,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120389977</v>
+        <v>120389972</v>
       </c>
       <c r="B61" t="n">
-        <v>86417</v>
+        <v>86325</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7275,25 +7275,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6037417</v>
+        <v>433</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius caesiocanescens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7302,17 +7302,17 @@
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>693846</v>
+        <v>693952</v>
       </c>
       <c r="R61" t="n">
-        <v>6360166</v>
+        <v>6360138</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7378,10 +7378,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120389972</v>
+        <v>120382898</v>
       </c>
       <c r="B62" t="n">
-        <v>86325</v>
+        <v>86302</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7394,37 +7394,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>693952</v>
+        <v>694010</v>
       </c>
       <c r="R62" t="n">
-        <v>6360138</v>
+        <v>6360337</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7454,19 +7451,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7481,22 +7468,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120382898</v>
+        <v>120390005</v>
       </c>
       <c r="B63" t="n">
-        <v>86302</v>
+        <v>90028</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7505,41 +7496,44 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>424</v>
+        <v>4191</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Kragjordstjärna</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Geastrum michelianum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Berk. &amp; Broome</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>694010</v>
+        <v>693948</v>
       </c>
       <c r="R63" t="n">
-        <v>6360337</v>
+        <v>6360161</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7566,9 +7560,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7583,26 +7587,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120390005</v>
+        <v>120389977</v>
       </c>
       <c r="B64" t="n">
-        <v>90028</v>
+        <v>86417</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7611,25 +7611,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4191</v>
+        <v>6037417</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kragjordstjärna</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Geastrum michelianum</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Berk. &amp; Broome</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7638,17 +7638,17 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693948</v>
+        <v>693846</v>
       </c>
       <c r="R64" t="n">
-        <v>6360161</v>
+        <v>6360166</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7935,10 +7935,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120382864</v>
+        <v>120382886</v>
       </c>
       <c r="B67" t="n">
-        <v>86449</v>
+        <v>86373</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7947,25 +7947,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7975,10 +7975,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>693969</v>
+        <v>694010</v>
       </c>
       <c r="R67" t="n">
-        <v>6360153</v>
+        <v>6360337</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8041,10 +8041,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120382886</v>
+        <v>120382864</v>
       </c>
       <c r="B68" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8053,25 +8053,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>694010</v>
+        <v>693969</v>
       </c>
       <c r="R68" t="n">
-        <v>6360337</v>
+        <v>6360153</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8147,10 +8147,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120382899</v>
+        <v>120382847</v>
       </c>
       <c r="B69" t="n">
-        <v>86302</v>
+        <v>90356</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8163,21 +8163,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>694017</v>
+        <v>693960</v>
       </c>
       <c r="R69" t="n">
-        <v>6360293</v>
+        <v>6360226</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120382847</v>
+        <v>120382888</v>
       </c>
       <c r="B70" t="n">
-        <v>90356</v>
+        <v>86373</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8269,21 +8269,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8293,10 +8293,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>693960</v>
+        <v>693806</v>
       </c>
       <c r="R70" t="n">
-        <v>6360226</v>
+        <v>6359993</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8359,10 +8359,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120382888</v>
+        <v>120382899</v>
       </c>
       <c r="B71" t="n">
-        <v>86373</v>
+        <v>86302</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8375,21 +8375,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8399,10 +8399,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>693806</v>
+        <v>694017</v>
       </c>
       <c r="R71" t="n">
-        <v>6359993</v>
+        <v>6360293</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9247,10 +9247,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120382863</v>
+        <v>120382853</v>
       </c>
       <c r="B79" t="n">
-        <v>86449</v>
+        <v>57336</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9263,21 +9263,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9287,10 +9287,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>693842</v>
+        <v>693992</v>
       </c>
       <c r="R79" t="n">
-        <v>6360049</v>
+        <v>6360385</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9353,10 +9353,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120389969</v>
+        <v>120382863</v>
       </c>
       <c r="B80" t="n">
-        <v>86302</v>
+        <v>86449</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9365,44 +9365,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>693949</v>
+        <v>693842</v>
       </c>
       <c r="R80" t="n">
-        <v>6360196</v>
+        <v>6360049</v>
       </c>
       <c r="S80" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9429,19 +9426,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9456,22 +9443,26 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120382853</v>
+        <v>120389969</v>
       </c>
       <c r="B81" t="n">
-        <v>57336</v>
+        <v>86302</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9480,41 +9471,44 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>424</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>693992</v>
+        <v>693949</v>
       </c>
       <c r="R81" t="n">
-        <v>6360385</v>
+        <v>6360196</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9541,9 +9535,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9558,19 +9562,15 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10029,10 +10029,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120390025</v>
+        <v>120390026</v>
       </c>
       <c r="B86" t="n">
-        <v>106214</v>
+        <v>106872</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10045,21 +10045,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10145,10 +10145,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120390026</v>
+        <v>120382862</v>
       </c>
       <c r="B87" t="n">
-        <v>106872</v>
+        <v>86449</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10161,38 +10161,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220079</v>
+        <v>6003295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>693824</v>
+        <v>694014</v>
       </c>
       <c r="R87" t="n">
-        <v>6360149</v>
+        <v>6360294</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10222,19 +10218,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:44</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10249,22 +10235,26 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120382893</v>
+        <v>120390025</v>
       </c>
       <c r="B88" t="n">
-        <v>89236</v>
+        <v>106214</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10273,38 +10263,42 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>245042</v>
+        <v>221849</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>693964</v>
+        <v>693824</v>
       </c>
       <c r="R88" t="n">
-        <v>6360133</v>
+        <v>6360149</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10334,9 +10328,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10351,26 +10355,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
-        </is>
-      </c>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120382862</v>
+        <v>120382893</v>
       </c>
       <c r="B89" t="n">
-        <v>86449</v>
+        <v>89236</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10379,25 +10379,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>245042</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10407,10 +10407,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>694014</v>
+        <v>693964</v>
       </c>
       <c r="R89" t="n">
-        <v>6360294</v>
+        <v>6360133</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12762,10 +12762,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120382132</v>
+        <v>120393451</v>
       </c>
       <c r="B111" t="n">
-        <v>86282</v>
+        <v>86302</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12774,44 +12774,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Vallagar norra (Vallhagar norra), Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>693977</v>
+        <v>694012</v>
       </c>
       <c r="R111" t="n">
-        <v>6360060</v>
+        <v>6360247</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12838,19 +12835,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12865,12 +12852,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -12991,10 +12978,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120393451</v>
+        <v>120382132</v>
       </c>
       <c r="B113" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13003,41 +12990,44 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>694012</v>
+        <v>693977</v>
       </c>
       <c r="R113" t="n">
-        <v>6360247</v>
+        <v>6360060</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -13064,9 +13054,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13081,12 +13081,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -13750,10 +13750,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120401499</v>
+        <v>120393448</v>
       </c>
       <c r="B120" t="n">
-        <v>86449</v>
+        <v>91854</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13762,41 +13762,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6003295</v>
+        <v>4363</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>694050</v>
+        <v>694027</v>
       </c>
       <c r="R120" t="n">
-        <v>6360251</v>
+        <v>6360257</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13837,19 +13834,18 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13860,10 +13856,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120401510</v>
+        <v>120401499</v>
       </c>
       <c r="B121" t="n">
-        <v>86302</v>
+        <v>86449</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13872,25 +13868,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13903,10 +13899,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>693932</v>
+        <v>694050</v>
       </c>
       <c r="R121" t="n">
-        <v>6360232</v>
+        <v>6360251</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13970,10 +13966,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120393448</v>
+        <v>120401510</v>
       </c>
       <c r="B122" t="n">
-        <v>91854</v>
+        <v>86302</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13982,38 +13978,41 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4363</v>
+        <v>424</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>694027</v>
+        <v>693932</v>
       </c>
       <c r="R122" t="n">
-        <v>6360257</v>
+        <v>6360232</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14054,18 +14053,19 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -4034,10 +4034,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120382147</v>
+        <v>120382854</v>
       </c>
       <c r="B32" t="n">
-        <v>90021</v>
+        <v>86282</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4050,40 +4050,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4188</v>
+        <v>3712</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vallagar norra (Vallhagar norra), Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>693925</v>
+        <v>694079</v>
       </c>
       <c r="R32" t="n">
-        <v>6360266</v>
+        <v>6360242</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,19 +4107,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4137,12 +4124,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4153,10 +4140,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120382854</v>
+        <v>120382147</v>
       </c>
       <c r="B33" t="n">
-        <v>86282</v>
+        <v>90021</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4169,37 +4156,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3712</v>
+        <v>4188</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>694079</v>
+        <v>693925</v>
       </c>
       <c r="R33" t="n">
-        <v>6360242</v>
+        <v>6360266</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4226,9 +4216,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4243,12 +4243,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5786,10 +5786,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120382897</v>
+        <v>120382142</v>
       </c>
       <c r="B48" t="n">
-        <v>86302</v>
+        <v>86414</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5798,41 +5798,44 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>424</v>
+        <v>3674</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>693971</v>
+        <v>693925</v>
       </c>
       <c r="R48" t="n">
-        <v>6360459</v>
+        <v>6360266</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5859,9 +5862,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5876,12 +5889,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5892,10 +5905,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120382142</v>
+        <v>120382888</v>
       </c>
       <c r="B49" t="n">
-        <v>86414</v>
+        <v>86373</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5904,44 +5917,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3674</v>
+        <v>248956</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Vallagar norra (Vallhagar norra), Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>693925</v>
+        <v>693806</v>
       </c>
       <c r="R49" t="n">
-        <v>6360266</v>
+        <v>6359993</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5968,19 +5978,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5995,12 +5995,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6011,10 +6011,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120382888</v>
+        <v>120382897</v>
       </c>
       <c r="B50" t="n">
-        <v>86373</v>
+        <v>86302</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6027,21 +6027,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>248956</v>
+        <v>424</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6051,10 +6051,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>693806</v>
+        <v>693971</v>
       </c>
       <c r="R50" t="n">
-        <v>6359993</v>
+        <v>6360459</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6342,10 +6342,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120382893</v>
+        <v>120382861</v>
       </c>
       <c r="B53" t="n">
-        <v>89236</v>
+        <v>86449</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6354,25 +6354,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>245042</v>
+        <v>6003295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6382,10 +6382,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693964</v>
+        <v>694007</v>
       </c>
       <c r="R53" t="n">
-        <v>6360133</v>
+        <v>6360345</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6448,10 +6448,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120382861</v>
+        <v>120382893</v>
       </c>
       <c r="B54" t="n">
-        <v>86449</v>
+        <v>89236</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6460,25 +6460,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6003295</v>
+        <v>245042</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>694007</v>
+        <v>693964</v>
       </c>
       <c r="R54" t="n">
-        <v>6360345</v>
+        <v>6360133</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7531,10 +7531,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120382881</v>
+        <v>120382891</v>
       </c>
       <c r="B64" t="n">
-        <v>85676</v>
+        <v>89236</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7547,21 +7547,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4852</v>
+        <v>245042</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kastanjefjällskivling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lepiota castanea</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>693945</v>
+        <v>693948</v>
       </c>
       <c r="R64" t="n">
-        <v>6360205</v>
+        <v>6360186</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7637,10 +7637,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120382891</v>
+        <v>120382881</v>
       </c>
       <c r="B65" t="n">
-        <v>89236</v>
+        <v>85676</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7653,21 +7653,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>245042</v>
+        <v>4852</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Kastanjefjällskivling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Lepiota castanea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7677,10 +7677,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>693948</v>
+        <v>693945</v>
       </c>
       <c r="R65" t="n">
-        <v>6360186</v>
+        <v>6360205</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7955,10 +7955,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120382899</v>
+        <v>120382146</v>
       </c>
       <c r="B68" t="n">
-        <v>86302</v>
+        <v>89236</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7967,41 +7967,44 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>424</v>
+        <v>245042</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>694017</v>
+        <v>693829</v>
       </c>
       <c r="R68" t="n">
-        <v>6360293</v>
+        <v>6360094</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8028,9 +8031,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8045,12 +8058,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8061,7 +8074,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120382146</v>
+        <v>120382895</v>
       </c>
       <c r="B69" t="n">
         <v>89236</v>
@@ -8095,22 +8108,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>693829</v>
+        <v>693867</v>
       </c>
       <c r="R69" t="n">
-        <v>6360094</v>
+        <v>6360109</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8137,19 +8147,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8164,12 +8164,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8180,10 +8180,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120382895</v>
+        <v>120382899</v>
       </c>
       <c r="B70" t="n">
-        <v>89236</v>
+        <v>86302</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8192,25 +8192,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>245042</v>
+        <v>424</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8220,10 +8220,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>693867</v>
+        <v>694017</v>
       </c>
       <c r="R70" t="n">
-        <v>6360109</v>
+        <v>6360293</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8286,10 +8286,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120401499</v>
+        <v>120401506</v>
       </c>
       <c r="B71" t="n">
-        <v>86449</v>
+        <v>86373</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8298,25 +8298,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8329,10 +8329,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>694050</v>
+        <v>693841</v>
       </c>
       <c r="R71" t="n">
-        <v>6360251</v>
+        <v>6360091</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8503,10 +8503,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120401506</v>
+        <v>120401499</v>
       </c>
       <c r="B73" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8515,25 +8515,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8546,10 +8546,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>693841</v>
+        <v>694050</v>
       </c>
       <c r="R73" t="n">
-        <v>6360091</v>
+        <v>6360251</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8842,10 +8842,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120393472</v>
+        <v>120401496</v>
       </c>
       <c r="B76" t="n">
-        <v>89236</v>
+        <v>86449</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8854,38 +8854,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>245042</v>
+        <v>6003295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>693978</v>
+        <v>693959</v>
       </c>
       <c r="R76" t="n">
-        <v>6360202</v>
+        <v>6360145</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8926,18 +8929,19 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8948,10 +8952,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120393449</v>
+        <v>120393472</v>
       </c>
       <c r="B77" t="n">
-        <v>90356</v>
+        <v>89236</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8960,25 +8964,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2015</v>
+        <v>245042</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8988,10 +8992,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>694058</v>
+        <v>693978</v>
       </c>
       <c r="R77" t="n">
-        <v>6360244</v>
+        <v>6360202</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9054,10 +9058,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120401496</v>
+        <v>120393449</v>
       </c>
       <c r="B78" t="n">
-        <v>86449</v>
+        <v>90356</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9066,41 +9070,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>693959</v>
+        <v>694058</v>
       </c>
       <c r="R78" t="n">
-        <v>6360145</v>
+        <v>6360244</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9141,19 +9142,18 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -10279,10 +10279,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120393452</v>
+        <v>120393454</v>
       </c>
       <c r="B89" t="n">
-        <v>86302</v>
+        <v>91870</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10291,25 +10291,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>424</v>
+        <v>4366</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10319,10 +10319,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>693937</v>
+        <v>694042</v>
       </c>
       <c r="R89" t="n">
-        <v>6360167</v>
+        <v>6360296</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10385,10 +10385,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120393454</v>
+        <v>120393452</v>
       </c>
       <c r="B90" t="n">
-        <v>91870</v>
+        <v>86302</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10397,25 +10397,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4366</v>
+        <v>424</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10425,10 +10425,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>694042</v>
+        <v>693937</v>
       </c>
       <c r="R90" t="n">
-        <v>6360296</v>
+        <v>6360167</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10491,10 +10491,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120393464</v>
+        <v>120401495</v>
       </c>
       <c r="B91" t="n">
-        <v>86373</v>
+        <v>86222</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10503,38 +10503,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>248956</v>
+        <v>3762</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>693925</v>
+        <v>693943</v>
       </c>
       <c r="R91" t="n">
-        <v>6360154</v>
+        <v>6360177</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10575,18 +10578,19 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10597,10 +10601,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120401495</v>
+        <v>120393464</v>
       </c>
       <c r="B92" t="n">
-        <v>86222</v>
+        <v>86373</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10609,41 +10613,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3762</v>
+        <v>248956</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>693943</v>
+        <v>693925</v>
       </c>
       <c r="R92" t="n">
-        <v>6360177</v>
+        <v>6360154</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10684,19 +10685,18 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11677,10 +11677,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120393458</v>
+        <v>120393466</v>
       </c>
       <c r="B102" t="n">
-        <v>86449</v>
+        <v>86367</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11689,25 +11689,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6003295</v>
+        <v>449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius fraudulosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11717,10 +11717,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693861</v>
+        <v>693834</v>
       </c>
       <c r="R102" t="n">
-        <v>6360098</v>
+        <v>6360067</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11783,7 +11783,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120393466</v>
+        <v>120393465</v>
       </c>
       <c r="B103" t="n">
         <v>86367</v>
@@ -11823,10 +11823,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693834</v>
+        <v>694019</v>
       </c>
       <c r="R103" t="n">
-        <v>6360067</v>
+        <v>6360356</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11889,10 +11889,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120393465</v>
+        <v>120393458</v>
       </c>
       <c r="B104" t="n">
-        <v>86367</v>
+        <v>86449</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11901,25 +11901,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>449</v>
+        <v>6003295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius fraudulosus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11929,10 +11929,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>694019</v>
+        <v>693861</v>
       </c>
       <c r="R104" t="n">
-        <v>6360356</v>
+        <v>6360098</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12976,10 +12976,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120487329</v>
+        <v>120488211</v>
       </c>
       <c r="B114" t="n">
-        <v>91872</v>
+        <v>86302</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12988,34 +12988,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>694057</v>
+        <v>694094</v>
       </c>
       <c r="R114" t="n">
-        <v>6359899</v>
+        <v>6359991</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13062,12 +13066,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -13078,10 +13082,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120487323</v>
+        <v>120487329</v>
       </c>
       <c r="B115" t="n">
-        <v>90351</v>
+        <v>91872</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13094,23 +13098,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3215</v>
+        <v>6047725</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -13118,10 +13118,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>694050</v>
+        <v>694057</v>
       </c>
       <c r="R115" t="n">
-        <v>6359916</v>
+        <v>6359899</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13184,10 +13184,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120487310</v>
+        <v>120487323</v>
       </c>
       <c r="B116" t="n">
-        <v>86302</v>
+        <v>90351</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13196,25 +13196,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>424</v>
+        <v>3215</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13224,10 +13224,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>693943</v>
+        <v>694050</v>
       </c>
       <c r="R116" t="n">
-        <v>6359926</v>
+        <v>6359916</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13290,10 +13290,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120389965</v>
+        <v>120487310</v>
       </c>
       <c r="B117" t="n">
-        <v>86282</v>
+        <v>86302</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13302,44 +13302,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>693783</v>
+        <v>693943</v>
       </c>
       <c r="R117" t="n">
-        <v>6360146</v>
+        <v>6359926</v>
       </c>
       <c r="S117" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13363,22 +13360,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13393,26 +13380,26 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120389980</v>
+        <v>120389965</v>
       </c>
       <c r="B118" t="n">
-        <v>86449</v>
+        <v>86282</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13421,25 +13408,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13452,13 +13439,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>693909</v>
+        <v>693783</v>
       </c>
       <c r="R118" t="n">
-        <v>6360231</v>
+        <v>6360146</v>
       </c>
       <c r="S118" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13487,7 +13474,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13497,7 +13484,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13528,10 +13515,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120488211</v>
+        <v>120389980</v>
       </c>
       <c r="B119" t="n">
-        <v>86302</v>
+        <v>86449</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13540,41 +13527,44 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>694094</v>
+        <v>693909</v>
       </c>
       <c r="R119" t="n">
-        <v>6359991</v>
+        <v>6360231</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13598,12 +13588,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13618,26 +13618,26 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120487384</v>
+        <v>120471223</v>
       </c>
       <c r="B120" t="n">
-        <v>100194</v>
+        <v>86373</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13646,38 +13646,41 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>222498</v>
+        <v>248956</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Hoxelmyr SO, Gtl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>694098</v>
+        <v>694058</v>
       </c>
       <c r="R120" t="n">
-        <v>6359944</v>
+        <v>6359975</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13724,12 +13727,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Suvi Sivula</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -13740,10 +13743,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120471223</v>
+        <v>120487384</v>
       </c>
       <c r="B121" t="n">
-        <v>86373</v>
+        <v>100194</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13752,41 +13755,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>248956</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Hoxelmyr SO, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>694058</v>
+        <v>694098</v>
       </c>
       <c r="R121" t="n">
-        <v>6359975</v>
+        <v>6359944</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13833,12 +13833,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -14706,10 +14706,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120487304</v>
+        <v>120488174</v>
       </c>
       <c r="B130" t="n">
-        <v>86302</v>
+        <v>86449</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14718,38 +14718,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>694225</v>
+        <v>694047</v>
       </c>
       <c r="R130" t="n">
-        <v>6359895</v>
+        <v>6359854</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14796,12 +14796,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -14812,10 +14812,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120488174</v>
+        <v>120487304</v>
       </c>
       <c r="B131" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14824,38 +14824,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>694047</v>
+        <v>694225</v>
       </c>
       <c r="R131" t="n">
-        <v>6359854</v>
+        <v>6359895</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14902,12 +14902,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -15663,10 +15663,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>120390006</v>
+        <v>120487327</v>
       </c>
       <c r="B139" t="n">
-        <v>90356</v>
+        <v>91872</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15675,44 +15675,37 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2015</v>
+        <v>6047725</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>693959</v>
+        <v>694114</v>
       </c>
       <c r="R139" t="n">
-        <v>6360193</v>
+        <v>6359932</v>
       </c>
       <c r="S139" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15736,22 +15729,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15766,26 +15749,26 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>120389966</v>
+        <v>120487380</v>
       </c>
       <c r="B140" t="n">
-        <v>86282</v>
+        <v>86417</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15794,44 +15777,41 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>3712</v>
+        <v>6037417</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>A.Ortega &amp; al.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>693948</v>
+        <v>694034</v>
       </c>
       <c r="R140" t="n">
-        <v>6360161</v>
+        <v>6359847</v>
       </c>
       <c r="S140" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15855,22 +15835,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15885,26 +15855,26 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>120487327</v>
+        <v>120487390</v>
       </c>
       <c r="B141" t="n">
-        <v>91872</v>
+        <v>100194</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15917,19 +15887,23 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6047725</v>
+        <v>222498</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15937,10 +15911,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>694114</v>
+        <v>693940</v>
       </c>
       <c r="R141" t="n">
-        <v>6359932</v>
+        <v>6359902</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16003,10 +15977,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>120487380</v>
+        <v>120487381</v>
       </c>
       <c r="B142" t="n">
-        <v>86417</v>
+        <v>86346</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16015,25 +15989,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6037417</v>
+        <v>442</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16043,10 +16017,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>694034</v>
+        <v>694252</v>
       </c>
       <c r="R142" t="n">
-        <v>6359847</v>
+        <v>6359924</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16109,10 +16083,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120487390</v>
+        <v>120487403</v>
       </c>
       <c r="B143" t="n">
-        <v>100194</v>
+        <v>86282</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16125,21 +16099,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222498</v>
+        <v>3712</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16149,10 +16123,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>693940</v>
+        <v>694080</v>
       </c>
       <c r="R143" t="n">
-        <v>6359902</v>
+        <v>6359907</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16215,10 +16189,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120487381</v>
+        <v>120390006</v>
       </c>
       <c r="B144" t="n">
-        <v>86346</v>
+        <v>90356</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16231,37 +16205,40 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>442</v>
+        <v>2015</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bullspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius corrosus</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>694252</v>
+        <v>693959</v>
       </c>
       <c r="R144" t="n">
-        <v>6359924</v>
+        <v>6360193</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16285,12 +16262,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16305,23 +16292,23 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120487403</v>
+        <v>120389966</v>
       </c>
       <c r="B145" t="n">
         <v>86282</v>
@@ -16355,19 +16342,22 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>694080</v>
+        <v>693948</v>
       </c>
       <c r="R145" t="n">
-        <v>6359907</v>
+        <v>6360161</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16391,12 +16381,22 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16411,26 +16411,26 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>120389981</v>
+        <v>120487383</v>
       </c>
       <c r="B146" t="n">
-        <v>86449</v>
+        <v>100194</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16439,44 +16439,41 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>693941</v>
+        <v>694180</v>
       </c>
       <c r="R146" t="n">
-        <v>6360226</v>
+        <v>6359892</v>
       </c>
       <c r="S146" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16500,22 +16497,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16530,26 +16517,26 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120389973</v>
+        <v>120389981</v>
       </c>
       <c r="B147" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16558,25 +16545,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16585,17 +16572,17 @@
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693812</v>
+        <v>693941</v>
       </c>
       <c r="R147" t="n">
-        <v>6360133</v>
+        <v>6360226</v>
       </c>
       <c r="S147" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16624,7 +16611,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16634,7 +16621,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16665,10 +16652,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120389967</v>
+        <v>120389973</v>
       </c>
       <c r="B148" t="n">
-        <v>86302</v>
+        <v>86373</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16681,21 +16668,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16704,17 +16691,17 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693946</v>
+        <v>693812</v>
       </c>
       <c r="R148" t="n">
-        <v>6360234</v>
+        <v>6360133</v>
       </c>
       <c r="S148" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16743,7 +16730,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16753,7 +16740,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16784,7 +16771,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120488870</v>
+        <v>120389967</v>
       </c>
       <c r="B149" t="n">
         <v>86302</v>
@@ -16817,29 +16804,23 @@
           <t>Kalchbr.</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>693984</v>
+        <v>693946</v>
       </c>
       <c r="R149" t="n">
-        <v>6359901</v>
+        <v>6360234</v>
       </c>
       <c r="S149" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16863,12 +16844,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16883,26 +16874,26 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120487383</v>
+        <v>120488870</v>
       </c>
       <c r="B150" t="n">
-        <v>100194</v>
+        <v>86302</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16911,41 +16902,50 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>222498</v>
+        <v>424</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>694180</v>
+        <v>693984</v>
       </c>
       <c r="R150" t="n">
-        <v>6359892</v>
+        <v>6359901</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16989,12 +16989,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -17429,10 +17429,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>120488867</v>
+        <v>120389977</v>
       </c>
       <c r="B155" t="n">
-        <v>90356</v>
+        <v>86417</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17441,50 +17441,44 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2015</v>
+        <v>6037417</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>694007</v>
+        <v>693846</v>
       </c>
       <c r="R155" t="n">
-        <v>6359952</v>
+        <v>6360166</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17508,12 +17502,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17528,26 +17532,26 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>120488876</v>
+        <v>120390025</v>
       </c>
       <c r="B156" t="n">
-        <v>86449</v>
+        <v>106214</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17560,46 +17564,41 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6003295</v>
+        <v>221849</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>694029</v>
+        <v>693824</v>
       </c>
       <c r="R156" t="n">
-        <v>6359927</v>
+        <v>6360149</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17623,12 +17622,22 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17643,26 +17652,26 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>120389977</v>
+        <v>120488867</v>
       </c>
       <c r="B157" t="n">
-        <v>86417</v>
+        <v>90356</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17671,44 +17680,50 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6037417</v>
+        <v>2015</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>693846</v>
+        <v>694007</v>
       </c>
       <c r="R157" t="n">
-        <v>6360166</v>
+        <v>6359952</v>
       </c>
       <c r="S157" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17732,22 +17747,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17762,26 +17767,26 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120390025</v>
+        <v>120488876</v>
       </c>
       <c r="B158" t="n">
-        <v>106214</v>
+        <v>86449</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17794,41 +17799,46 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221849</v>
+        <v>6003295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>693824</v>
+        <v>694029</v>
       </c>
       <c r="R158" t="n">
-        <v>6360149</v>
+        <v>6359927</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17852,22 +17862,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17882,17 +17882,17 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
@@ -18126,10 +18126,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>120488868</v>
+        <v>120487349</v>
       </c>
       <c r="B161" t="n">
-        <v>90356</v>
+        <v>86449</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -18138,50 +18138,41 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>694273</v>
+        <v>694206</v>
       </c>
       <c r="R161" t="n">
         <v>6359895</v>
       </c>
       <c r="S161" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18225,12 +18216,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -18241,10 +18232,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120487349</v>
+        <v>120487301</v>
       </c>
       <c r="B162" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18253,25 +18244,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18281,10 +18272,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>694206</v>
+        <v>694093</v>
       </c>
       <c r="R162" t="n">
-        <v>6359895</v>
+        <v>6359997</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18347,10 +18338,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120487301</v>
+        <v>120488868</v>
       </c>
       <c r="B163" t="n">
-        <v>86302</v>
+        <v>90356</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18363,37 +18354,46 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>694093</v>
+        <v>694273</v>
       </c>
       <c r="R163" t="n">
-        <v>6359997</v>
+        <v>6359895</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18437,12 +18437,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -20184,10 +20184,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120487373</v>
+        <v>120389972</v>
       </c>
       <c r="B180" t="n">
-        <v>86373</v>
+        <v>86325</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -20200,34 +20200,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius caesiocanescens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>694166</v>
+        <v>693952</v>
       </c>
       <c r="R180" t="n">
-        <v>6359992</v>
+        <v>6360138</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20254,12 +20257,22 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20274,23 +20287,23 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120487351</v>
+        <v>120389979</v>
       </c>
       <c r="B181" t="n">
         <v>86449</v>
@@ -20324,19 +20337,22 @@
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>694004</v>
+        <v>693831</v>
       </c>
       <c r="R181" t="n">
-        <v>6359932</v>
+        <v>6360180</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -20360,12 +20376,22 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20380,26 +20406,26 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120389972</v>
+        <v>120488883</v>
       </c>
       <c r="B182" t="n">
-        <v>86325</v>
+        <v>86373</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20412,40 +20438,46 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>433</v>
+        <v>248956</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>693952</v>
+        <v>694326</v>
       </c>
       <c r="R182" t="n">
-        <v>6360138</v>
+        <v>6359908</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20469,22 +20501,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20499,26 +20521,26 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120389979</v>
+        <v>120487373</v>
       </c>
       <c r="B183" t="n">
-        <v>86449</v>
+        <v>86373</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20527,44 +20549,41 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>693831</v>
+        <v>694166</v>
       </c>
       <c r="R183" t="n">
-        <v>6360180</v>
+        <v>6359992</v>
       </c>
       <c r="S183" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20588,22 +20607,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>10:48</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20618,26 +20627,26 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120488883</v>
+        <v>120487351</v>
       </c>
       <c r="B184" t="n">
-        <v>86373</v>
+        <v>86449</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20646,50 +20655,41 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>248956</v>
+        <v>6003295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>694326</v>
+        <v>694004</v>
       </c>
       <c r="R184" t="n">
-        <v>6359908</v>
+        <v>6359932</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -20733,12 +20733,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -21176,10 +21176,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120488197</v>
+        <v>120390026</v>
       </c>
       <c r="B189" t="n">
-        <v>89236</v>
+        <v>106872</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -21188,38 +21188,42 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>245042</v>
+        <v>220079</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>694010</v>
+        <v>693824</v>
       </c>
       <c r="R189" t="n">
-        <v>6359833</v>
+        <v>6360149</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21246,12 +21250,22 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21260,33 +21274,32 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>120487409</v>
+        <v>120390004</v>
       </c>
       <c r="B190" t="n">
-        <v>89236</v>
+        <v>90021</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21299,37 +21312,40 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>245042</v>
+        <v>4188</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Fr.:Pers.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>694034</v>
+        <v>693783</v>
       </c>
       <c r="R190" t="n">
-        <v>6359847</v>
+        <v>6360146</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -21353,12 +21369,22 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21373,26 +21399,26 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>120471220</v>
+        <v>120389974</v>
       </c>
       <c r="B191" t="n">
-        <v>86302</v>
+        <v>86373</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21405,21 +21431,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>424</v>
+        <v>248956</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21428,17 +21454,17 @@
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Hoxelmyr SO, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>694050</v>
+        <v>693816</v>
       </c>
       <c r="R191" t="n">
-        <v>6359945</v>
+        <v>6360164</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21462,12 +21488,22 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21482,26 +21518,26 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Suvi Sivula</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>120390026</v>
+        <v>120488197</v>
       </c>
       <c r="B192" t="n">
-        <v>106872</v>
+        <v>89236</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21510,42 +21546,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220079</v>
+        <v>245042</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>693824</v>
+        <v>694010</v>
       </c>
       <c r="R192" t="n">
-        <v>6360149</v>
+        <v>6359833</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21572,22 +21604,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21596,32 +21618,33 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>120390004</v>
+        <v>120471220</v>
       </c>
       <c r="B193" t="n">
-        <v>90021</v>
+        <v>86302</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21630,25 +21653,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4188</v>
+        <v>424</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21657,17 +21680,17 @@
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Hoxelmyr SO, Gtl</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>693783</v>
+        <v>694050</v>
       </c>
       <c r="R193" t="n">
-        <v>6360146</v>
+        <v>6359945</v>
       </c>
       <c r="S193" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -21691,22 +21714,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21721,26 +21734,26 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Suvi Sivula</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Suvi Sivula, Stefan Phalagorn Bergström</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>120389974</v>
+        <v>120487409</v>
       </c>
       <c r="B194" t="n">
-        <v>86373</v>
+        <v>89236</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21749,44 +21762,41 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>693816</v>
+        <v>694034</v>
       </c>
       <c r="R194" t="n">
-        <v>6360164</v>
+        <v>6359847</v>
       </c>
       <c r="S194" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21810,22 +21820,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21840,17 +21840,17 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -4034,10 +4034,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120382877</v>
+        <v>120382145</v>
       </c>
       <c r="B32" t="n">
-        <v>97908</v>
+        <v>89236</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4050,37 +4050,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>245042</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fröjel Sälle, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>694046</v>
+        <v>694045</v>
       </c>
       <c r="R32" t="n">
-        <v>6360376</v>
+        <v>6360164</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4107,9 +4110,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4124,12 +4137,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4140,10 +4153,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120382145</v>
+        <v>120382877</v>
       </c>
       <c r="B33" t="n">
-        <v>89236</v>
+        <v>97908</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4156,40 +4169,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>245042</v>
+        <v>219798</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vallagar norra (Vallhagar norra), Gtl</t>
+          <t>Fröjel Sälle, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>694045</v>
+        <v>694046</v>
       </c>
       <c r="R33" t="n">
-        <v>6360164</v>
+        <v>6360376</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4216,19 +4226,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4243,12 +4243,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5133,10 +5133,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120382894</v>
+        <v>120382861</v>
       </c>
       <c r="B42" t="n">
-        <v>89236</v>
+        <v>86449</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5145,25 +5145,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>245042</v>
+        <v>6003295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>694014</v>
+        <v>694007</v>
       </c>
       <c r="R42" t="n">
-        <v>6360338</v>
+        <v>6360345</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5239,10 +5239,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120382861</v>
+        <v>120382894</v>
       </c>
       <c r="B43" t="n">
-        <v>86449</v>
+        <v>89236</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5251,25 +5251,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6003295</v>
+        <v>245042</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5279,10 +5279,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>694007</v>
+        <v>694014</v>
       </c>
       <c r="R43" t="n">
-        <v>6360345</v>
+        <v>6360338</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5875,10 +5875,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120382858</v>
+        <v>120382900</v>
       </c>
       <c r="B49" t="n">
-        <v>91872</v>
+        <v>86302</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5887,23 +5887,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5911,10 +5915,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>694046</v>
+        <v>693947</v>
       </c>
       <c r="R49" t="n">
-        <v>6360382</v>
+        <v>6360230</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5955,7 +5959,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5978,7 +5981,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120382900</v>
+        <v>120382899</v>
       </c>
       <c r="B50" t="n">
         <v>86302</v>
@@ -6018,10 +6021,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>693947</v>
+        <v>694017</v>
       </c>
       <c r="R50" t="n">
-        <v>6360230</v>
+        <v>6360293</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6084,7 +6087,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120382899</v>
+        <v>120382896</v>
       </c>
       <c r="B51" t="n">
         <v>86302</v>
@@ -6124,10 +6127,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>694017</v>
+        <v>694015</v>
       </c>
       <c r="R51" t="n">
-        <v>6360293</v>
+        <v>6360173</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6190,10 +6193,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120382896</v>
+        <v>120382858</v>
       </c>
       <c r="B52" t="n">
-        <v>86302</v>
+        <v>91872</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6202,27 +6205,23 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>424</v>
+        <v>6047725</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6230,10 +6229,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>694015</v>
+        <v>694046</v>
       </c>
       <c r="R52" t="n">
-        <v>6360173</v>
+        <v>6360382</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6274,6 +6273,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6296,10 +6296,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120382848</v>
+        <v>120382888</v>
       </c>
       <c r="B53" t="n">
-        <v>90356</v>
+        <v>86373</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6312,21 +6312,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2015</v>
+        <v>248956</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>693804</v>
+        <v>693806</v>
       </c>
       <c r="R53" t="n">
-        <v>6360012</v>
+        <v>6359993</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,10 +6402,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120382888</v>
+        <v>120382848</v>
       </c>
       <c r="B54" t="n">
-        <v>86373</v>
+        <v>90356</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6418,21 +6418,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>248956</v>
+        <v>2015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6442,10 +6442,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>693806</v>
+        <v>693804</v>
       </c>
       <c r="R54" t="n">
-        <v>6359993</v>
+        <v>6360012</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6746,10 +6746,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120382864</v>
+        <v>120382857</v>
       </c>
       <c r="B57" t="n">
-        <v>86449</v>
+        <v>90351</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6758,25 +6758,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6003295</v>
+        <v>3215</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>693969</v>
+        <v>693914</v>
       </c>
       <c r="R57" t="n">
-        <v>6360153</v>
+        <v>6360179</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6852,10 +6852,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120382857</v>
+        <v>120382864</v>
       </c>
       <c r="B58" t="n">
-        <v>90351</v>
+        <v>86449</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6864,25 +6864,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3215</v>
+        <v>6003295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>693914</v>
+        <v>693969</v>
       </c>
       <c r="R58" t="n">
-        <v>6360179</v>
+        <v>6360153</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -9693,10 +9693,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120401496</v>
+        <v>120393449</v>
       </c>
       <c r="B84" t="n">
-        <v>86449</v>
+        <v>90356</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9705,41 +9705,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>693959</v>
+        <v>694058</v>
       </c>
       <c r="R84" t="n">
-        <v>6360145</v>
+        <v>6360244</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9780,19 +9777,18 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9803,10 +9799,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120393449</v>
+        <v>120401496</v>
       </c>
       <c r="B85" t="n">
-        <v>90356</v>
+        <v>86449</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9815,38 +9811,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>694058</v>
+        <v>693959</v>
       </c>
       <c r="R85" t="n">
-        <v>6360244</v>
+        <v>6360145</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9887,18 +9886,19 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -11549,10 +11549,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120393455</v>
+        <v>120382149</v>
       </c>
       <c r="B101" t="n">
-        <v>86222</v>
+        <v>90060</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11561,41 +11561,44 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3762</v>
+        <v>3286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>694018</v>
+        <v>693887</v>
       </c>
       <c r="R101" t="n">
-        <v>6360242</v>
+        <v>6360046</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11622,9 +11625,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11639,12 +11652,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11655,10 +11668,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120382149</v>
+        <v>120401504</v>
       </c>
       <c r="B102" t="n">
-        <v>90060</v>
+        <v>86373</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11667,25 +11680,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3286</v>
+        <v>248956</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11694,17 +11707,17 @@
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Vallagar norra (Vallhagar norra), Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>693887</v>
+        <v>693797</v>
       </c>
       <c r="R102" t="n">
-        <v>6360046</v>
+        <v>6359993</v>
       </c>
       <c r="S102" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11731,39 +11744,30 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -11774,10 +11778,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120401504</v>
+        <v>120382133</v>
       </c>
       <c r="B103" t="n">
-        <v>86373</v>
+        <v>86325</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11790,21 +11794,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>248956</v>
+        <v>433</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius caesiocanescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11813,17 +11817,17 @@
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Vallagar norra (Vallhagar norra), Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>693797</v>
+        <v>693977</v>
       </c>
       <c r="R103" t="n">
-        <v>6359993</v>
+        <v>6360060</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11850,30 +11854,39 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Majken Ekstrand</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11884,10 +11897,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120382133</v>
+        <v>120393452</v>
       </c>
       <c r="B104" t="n">
-        <v>86325</v>
+        <v>86302</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11900,40 +11913,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Vallagar norra (Vallhagar norra), Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>693977</v>
+        <v>693937</v>
       </c>
       <c r="R104" t="n">
-        <v>6360060</v>
+        <v>6360167</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11960,19 +11970,9 @@
           <t>2024-10-13</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11987,12 +11987,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Majken Ekstrand</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12003,10 +12003,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120393452</v>
+        <v>120393467</v>
       </c>
       <c r="B105" t="n">
-        <v>86302</v>
+        <v>86282</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12015,25 +12015,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12043,10 +12043,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>693937</v>
+        <v>693930</v>
       </c>
       <c r="R105" t="n">
-        <v>6360167</v>
+        <v>6360168</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12109,10 +12109,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120393467</v>
+        <v>120393455</v>
       </c>
       <c r="B106" t="n">
-        <v>86282</v>
+        <v>86222</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12125,21 +12125,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3712</v>
+        <v>3762</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12149,10 +12149,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>693930</v>
+        <v>694018</v>
       </c>
       <c r="R106" t="n">
-        <v>6360168</v>
+        <v>6360242</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12215,10 +12215,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120401490</v>
+        <v>120393458</v>
       </c>
       <c r="B107" t="n">
-        <v>90356</v>
+        <v>86449</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12227,41 +12227,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2015</v>
+        <v>6003295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Vallhagar norra, Gtl</t>
+          <t>Fröjel, Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>694015</v>
+        <v>693861</v>
       </c>
       <c r="R107" t="n">
-        <v>6360329</v>
+        <v>6360098</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12302,19 +12299,18 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -12325,10 +12321,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120393458</v>
+        <v>120401490</v>
       </c>
       <c r="B108" t="n">
-        <v>86449</v>
+        <v>90356</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12337,38 +12333,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6003295</v>
+        <v>2015</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fröjel, Gtl</t>
+          <t>Vallhagar norra, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>693861</v>
+        <v>694015</v>
       </c>
       <c r="R108" t="n">
-        <v>6360098</v>
+        <v>6360329</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12409,18 +12408,19 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Petra Wikström, Mattias Andersson, Anna Helmersson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -14869,10 +14869,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120487372</v>
+        <v>120487320</v>
       </c>
       <c r="B131" t="n">
-        <v>86373</v>
+        <v>57336</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14881,25 +14881,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>248956</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14909,10 +14909,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>694107</v>
+        <v>694185</v>
       </c>
       <c r="R131" t="n">
-        <v>6359997</v>
+        <v>6359895</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15081,10 +15081,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120487347</v>
+        <v>120487372</v>
       </c>
       <c r="B133" t="n">
-        <v>86449</v>
+        <v>86373</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15093,25 +15093,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15121,10 +15121,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>694251</v>
+        <v>694107</v>
       </c>
       <c r="R133" t="n">
-        <v>6359909</v>
+        <v>6359997</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15187,10 +15187,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120487351</v>
+        <v>120488212</v>
       </c>
       <c r="B134" t="n">
-        <v>86449</v>
+        <v>86302</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15199,38 +15199,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6003295</v>
+        <v>424</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>694004</v>
+        <v>693986</v>
       </c>
       <c r="R134" t="n">
-        <v>6359932</v>
+        <v>6359810</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15277,12 +15277,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -15293,10 +15293,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120488212</v>
+        <v>120487347</v>
       </c>
       <c r="B135" t="n">
-        <v>86302</v>
+        <v>86449</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15305,38 +15305,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>424</v>
+        <v>6003295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>693986</v>
+        <v>694251</v>
       </c>
       <c r="R135" t="n">
-        <v>6359810</v>
+        <v>6359909</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15383,12 +15383,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -15399,10 +15399,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>120487320</v>
+        <v>120487351</v>
       </c>
       <c r="B136" t="n">
-        <v>57336</v>
+        <v>86449</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15415,21 +15415,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100049</v>
+        <v>6003295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15439,10 +15439,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>694185</v>
+        <v>694004</v>
       </c>
       <c r="R136" t="n">
-        <v>6359895</v>
+        <v>6359932</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16163,10 +16163,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>120487327</v>
+        <v>120488870</v>
       </c>
       <c r="B143" t="n">
-        <v>91872</v>
+        <v>86302</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16175,37 +16175,50 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6047725</v>
+        <v>424</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>694114</v>
+        <v>693984</v>
       </c>
       <c r="R143" t="n">
-        <v>6359932</v>
+        <v>6359901</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16249,12 +16262,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -16265,10 +16278,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>120488870</v>
+        <v>120488868</v>
       </c>
       <c r="B144" t="n">
-        <v>86302</v>
+        <v>90356</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16281,21 +16294,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -16314,10 +16327,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>693984</v>
+        <v>694273</v>
       </c>
       <c r="R144" t="n">
-        <v>6359901</v>
+        <v>6359895</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -16380,10 +16393,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>120488868</v>
+        <v>120487327</v>
       </c>
       <c r="B145" t="n">
-        <v>90356</v>
+        <v>91872</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16392,50 +16405,37 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2015</v>
+        <v>6047725</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>694273</v>
+        <v>694114</v>
       </c>
       <c r="R145" t="n">
-        <v>6359895</v>
+        <v>6359932</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16479,12 +16479,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -16601,10 +16601,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>120389985</v>
+        <v>120389982</v>
       </c>
       <c r="B147" t="n">
-        <v>86465</v>
+        <v>86449</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16613,25 +16613,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>248947</v>
+        <v>6003295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16644,13 +16644,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>693944</v>
+        <v>693945</v>
       </c>
       <c r="R147" t="n">
-        <v>6360120</v>
+        <v>6360147</v>
       </c>
       <c r="S147" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16720,10 +16720,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>120389982</v>
+        <v>120389972</v>
       </c>
       <c r="B148" t="n">
-        <v>86449</v>
+        <v>86325</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16732,25 +16732,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6003295</v>
+        <v>433</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius caesiocanescens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16763,13 +16763,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>693945</v>
+        <v>693952</v>
       </c>
       <c r="R148" t="n">
-        <v>6360147</v>
+        <v>6360138</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16808,7 +16808,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16839,10 +16839,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>120389972</v>
+        <v>120390006</v>
       </c>
       <c r="B149" t="n">
-        <v>86325</v>
+        <v>90356</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16855,21 +16855,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>433</v>
+        <v>2015</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>M. M. Moser</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16882,13 +16882,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>693952</v>
+        <v>693959</v>
       </c>
       <c r="R149" t="n">
-        <v>6360138</v>
+        <v>6360193</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16958,10 +16958,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>120390006</v>
+        <v>120389985</v>
       </c>
       <c r="B150" t="n">
-        <v>90356</v>
+        <v>86465</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16970,25 +16970,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2015</v>
+        <v>248947</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -17001,13 +17001,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>693959</v>
+        <v>693944</v>
       </c>
       <c r="R150" t="n">
-        <v>6360193</v>
+        <v>6360120</v>
       </c>
       <c r="S150" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17850,10 +17850,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>120487304</v>
+        <v>120487278</v>
       </c>
       <c r="B158" t="n">
-        <v>86302</v>
+        <v>90356</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17866,21 +17866,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>424</v>
+        <v>2015</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17890,10 +17890,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>694225</v>
+        <v>694315</v>
       </c>
       <c r="R158" t="n">
-        <v>6359895</v>
+        <v>6359896</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17956,10 +17956,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>120487278</v>
+        <v>120487304</v>
       </c>
       <c r="B159" t="n">
-        <v>90356</v>
+        <v>86302</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17972,21 +17972,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2015</v>
+        <v>424</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Peck</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17996,10 +17996,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>694315</v>
+        <v>694225</v>
       </c>
       <c r="R159" t="n">
-        <v>6359896</v>
+        <v>6359895</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18062,10 +18062,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>120390004</v>
+        <v>120488871</v>
       </c>
       <c r="B160" t="n">
-        <v>90021</v>
+        <v>86302</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -18074,44 +18074,50 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4188</v>
+        <v>424</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fransig jordstjärna</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Geastrum fimbriatum</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Fr.:Pers.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>693783</v>
+        <v>694284</v>
       </c>
       <c r="R160" t="n">
-        <v>6360146</v>
+        <v>6359908</v>
       </c>
       <c r="S160" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18135,22 +18141,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>10:41</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18165,17 +18161,17 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
@@ -18287,10 +18283,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>120488871</v>
+        <v>120390004</v>
       </c>
       <c r="B162" t="n">
-        <v>86302</v>
+        <v>90021</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -18299,50 +18295,44 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>424</v>
+        <v>4188</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>694284</v>
+        <v>693783</v>
       </c>
       <c r="R162" t="n">
-        <v>6359908</v>
+        <v>6360146</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18366,12 +18356,22 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18386,26 +18386,26 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>120389966</v>
+        <v>120488168</v>
       </c>
       <c r="B163" t="n">
-        <v>86282</v>
+        <v>86449</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18414,44 +18414,41 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3712</v>
+        <v>6003295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Vallhagar, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>693948</v>
+        <v>694005</v>
       </c>
       <c r="R163" t="n">
-        <v>6360161</v>
+        <v>6359829</v>
       </c>
       <c r="S163" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18475,22 +18472,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18499,32 +18486,33 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>120487323</v>
+        <v>120487331</v>
       </c>
       <c r="B164" t="n">
-        <v>90351</v>
+        <v>91872</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18537,23 +18525,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3215</v>
+        <v>6047725</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
@@ -18561,10 +18545,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>694050</v>
+        <v>694012</v>
       </c>
       <c r="R164" t="n">
-        <v>6359916</v>
+        <v>6359847</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18627,10 +18611,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>120487403</v>
+        <v>120487375</v>
       </c>
       <c r="B165" t="n">
-        <v>86282</v>
+        <v>86373</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18639,25 +18623,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3712</v>
+        <v>248956</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18667,10 +18651,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>694080</v>
+        <v>694292</v>
       </c>
       <c r="R165" t="n">
-        <v>6359907</v>
+        <v>6359914</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18733,10 +18717,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>120487375</v>
+        <v>120487408</v>
       </c>
       <c r="B166" t="n">
-        <v>86373</v>
+        <v>89236</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18745,25 +18729,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18773,10 +18757,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>694292</v>
+        <v>694199</v>
       </c>
       <c r="R166" t="n">
-        <v>6359914</v>
+        <v>6359895</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18839,10 +18823,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>120487408</v>
+        <v>120487390</v>
       </c>
       <c r="B167" t="n">
-        <v>89236</v>
+        <v>100194</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18855,21 +18839,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>245042</v>
+        <v>222498</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18879,10 +18863,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>694199</v>
+        <v>693940</v>
       </c>
       <c r="R167" t="n">
-        <v>6359895</v>
+        <v>6359902</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18945,10 +18929,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>120488168</v>
+        <v>120487323</v>
       </c>
       <c r="B168" t="n">
-        <v>86449</v>
+        <v>90351</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18957,38 +18941,38 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6003295</v>
+        <v>3215</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>694005</v>
+        <v>694050</v>
       </c>
       <c r="R168" t="n">
-        <v>6359829</v>
+        <v>6359916</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19029,19 +19013,18 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -19052,10 +19035,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>120487390</v>
+        <v>120487403</v>
       </c>
       <c r="B169" t="n">
-        <v>100194</v>
+        <v>86282</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19068,21 +19051,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>222498</v>
+        <v>3712</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -19092,10 +19075,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>693940</v>
+        <v>694080</v>
       </c>
       <c r="R169" t="n">
-        <v>6359902</v>
+        <v>6359907</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19158,10 +19141,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>120487331</v>
+        <v>120389966</v>
       </c>
       <c r="B170" t="n">
-        <v>91872</v>
+        <v>86282</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19174,33 +19157,40 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6047725</v>
+        <v>3712</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr"/>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Vallhagar, Gtl</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>694012</v>
+        <v>693948</v>
       </c>
       <c r="R170" t="n">
-        <v>6359847</v>
+        <v>6360161</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19224,12 +19214,22 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19244,17 +19244,17 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
@@ -20780,10 +20780,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120488867</v>
+        <v>120390026</v>
       </c>
       <c r="B185" t="n">
-        <v>90356</v>
+        <v>106872</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20792,50 +20792,45 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2015</v>
+        <v>220079</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vit taggsvamp</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnum albidum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Peck</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Hoxelmyr, Gtl</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>694007</v>
+        <v>693824</v>
       </c>
       <c r="R185" t="n">
-        <v>6359952</v>
+        <v>6360149</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -20859,12 +20854,22 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20879,26 +20884,26 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Åsa Kestrup</t>
+          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>Naturhänsyns Gotlandsträff 2024</t>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120390026</v>
+        <v>120487373</v>
       </c>
       <c r="B186" t="n">
-        <v>106872</v>
+        <v>86373</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20907,42 +20912,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220079</v>
+        <v>248956</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Hoxelmyr, Gtl</t>
+          <t>Väst om Ansarve, Gtl</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>693824</v>
+        <v>694166</v>
       </c>
       <c r="R186" t="n">
-        <v>6360149</v>
+        <v>6359992</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20969,22 +20970,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>10:44</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20999,26 +20990,26 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isabelle Severholt, Birgitta Wasstorp, Majken Ekstrand, Martin Axegård, Mattias Andersson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
+          <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120487373</v>
+        <v>120487410</v>
       </c>
       <c r="B187" t="n">
-        <v>86373</v>
+        <v>89236</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21027,25 +21018,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>248956</v>
+        <v>245042</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -21055,10 +21046,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>694166</v>
+        <v>693992</v>
       </c>
       <c r="R187" t="n">
-        <v>6359992</v>
+        <v>6359939</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21121,10 +21112,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120487410</v>
+        <v>120488867</v>
       </c>
       <c r="B188" t="n">
-        <v>89236</v>
+        <v>90356</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21133,41 +21124,50 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>245042</v>
+        <v>2015</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Väst om Ansarve, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>693992</v>
+        <v>694007</v>
       </c>
       <c r="R188" t="n">
-        <v>6359939</v>
+        <v>6359952</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21211,12 +21211,12 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Åsa Kestrup</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY206"/>
+  <dimension ref="A1:AY222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22459,7 +22459,7 @@
         <v>126697989</v>
       </c>
       <c r="B200" t="n">
-        <v>106654</v>
+        <v>106729</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>126697541</v>
       </c>
       <c r="B201" t="n">
-        <v>98389</v>
+        <v>98464</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>126697967</v>
       </c>
       <c r="B202" t="n">
-        <v>110242</v>
+        <v>110317</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>126697723</v>
       </c>
       <c r="B203" t="n">
-        <v>98336</v>
+        <v>98411</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>126697982</v>
       </c>
       <c r="B205" t="n">
-        <v>98389</v>
+        <v>98464</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23312,6 +23312,1717 @@
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>127295445</v>
+      </c>
+      <c r="B207" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>693797</v>
+      </c>
+      <c r="R207" t="n">
+        <v>6360122</v>
+      </c>
+      <c r="S207" t="n">
+        <v>5</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI207" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>127295652</v>
+      </c>
+      <c r="B208" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>693786</v>
+      </c>
+      <c r="R208" t="n">
+        <v>6360073</v>
+      </c>
+      <c r="S208" t="n">
+        <v>5</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>127296656</v>
+      </c>
+      <c r="B209" t="n">
+        <v>57459</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>693805</v>
+      </c>
+      <c r="R209" t="n">
+        <v>6360191</v>
+      </c>
+      <c r="S209" t="n">
+        <v>10</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken; trolig häckning i området.</t>
+        </is>
+      </c>
+      <c r="AD209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>127295449</v>
+      </c>
+      <c r="B210" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>693796</v>
+      </c>
+      <c r="R210" t="n">
+        <v>6360105</v>
+      </c>
+      <c r="S210" t="n">
+        <v>5</v>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX210" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>127295427</v>
+      </c>
+      <c r="B211" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>693766</v>
+      </c>
+      <c r="R211" t="n">
+        <v>6360053</v>
+      </c>
+      <c r="S211" t="n">
+        <v>5</v>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W211" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y211" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Kalkbrott 5 m NV.</t>
+        </is>
+      </c>
+      <c r="AD211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI211" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>127295437</v>
+      </c>
+      <c r="B212" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>693848</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6360185</v>
+      </c>
+      <c r="S212" t="n">
+        <v>5</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX212" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>127295426</v>
+      </c>
+      <c r="B213" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>693766</v>
+      </c>
+      <c r="R213" t="n">
+        <v>6360053</v>
+      </c>
+      <c r="S213" t="n">
+        <v>5</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Kalkbrott 5 m NV.</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>127295453</v>
+      </c>
+      <c r="B214" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>693795</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6360053</v>
+      </c>
+      <c r="S214" t="n">
+        <v>5</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>127295436</v>
+      </c>
+      <c r="B215" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>693858</v>
+      </c>
+      <c r="R215" t="n">
+        <v>6360185</v>
+      </c>
+      <c r="S215" t="n">
+        <v>5</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>127295442</v>
+      </c>
+      <c r="B216" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>693767</v>
+      </c>
+      <c r="R216" t="n">
+        <v>6360139</v>
+      </c>
+      <c r="S216" t="n">
+        <v>5</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>127295455</v>
+      </c>
+      <c r="B217" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>693777</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6360032</v>
+      </c>
+      <c r="S217" t="n">
+        <v>5</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
+        </is>
+      </c>
+      <c r="AD217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>127295429</v>
+      </c>
+      <c r="B218" t="n">
+        <v>109260</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>693796</v>
+      </c>
+      <c r="R218" t="n">
+        <v>6360056</v>
+      </c>
+      <c r="S218" t="n">
+        <v>5</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>127295432</v>
+      </c>
+      <c r="B219" t="n">
+        <v>107318</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>693813</v>
+      </c>
+      <c r="R219" t="n">
+        <v>6360058</v>
+      </c>
+      <c r="S219" t="n">
+        <v>5</v>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W219" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y219" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG219" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI219" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT219" t="inlineStr"/>
+      <c r="AW219" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>127295447</v>
+      </c>
+      <c r="B220" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>693788</v>
+      </c>
+      <c r="R220" t="n">
+        <v>6360120</v>
+      </c>
+      <c r="S220" t="n">
+        <v>5</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI220" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX220" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>127295440</v>
+      </c>
+      <c r="B221" t="n">
+        <v>106729</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>693771</v>
+      </c>
+      <c r="R221" t="n">
+        <v>6360172</v>
+      </c>
+      <c r="S221" t="n">
+        <v>5</v>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT221" t="inlineStr"/>
+      <c r="AW221" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX221" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>127295443</v>
+      </c>
+      <c r="B222" t="n">
+        <v>102569</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>693783</v>
+      </c>
+      <c r="R222" t="n">
+        <v>6360120</v>
+      </c>
+      <c r="S222" t="n">
+        <v>5</v>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W222" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y222" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Liten planta, 40 cm, något osäker.</t>
+        </is>
+      </c>
+      <c r="AD222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG222" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI222" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, kalkberg.</t>
+        </is>
+      </c>
+      <c r="AT222" t="inlineStr"/>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -22459,7 +22459,7 @@
         <v>126697989</v>
       </c>
       <c r="B200" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>126697541</v>
       </c>
       <c r="B201" t="n">
-        <v>98464</v>
+        <v>98470</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>126697967</v>
       </c>
       <c r="B202" t="n">
-        <v>110317</v>
+        <v>110323</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>126697723</v>
       </c>
       <c r="B203" t="n">
-        <v>98411</v>
+        <v>98417</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>126697982</v>
       </c>
       <c r="B205" t="n">
-        <v>98464</v>
+        <v>98470</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23954,10 +23954,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127295426</v>
+        <v>127295453</v>
       </c>
       <c r="B213" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>693766</v>
+        <v>693795</v>
       </c>
       <c r="R213" t="n">
         <v>6360053</v>
@@ -24025,11 +24025,6 @@
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Kalkbrott 5 m NV.</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24061,10 +24056,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127295453</v>
+        <v>127295426</v>
       </c>
       <c r="B214" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24096,7 +24091,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>693795</v>
+        <v>693766</v>
       </c>
       <c r="R214" t="n">
         <v>6360053</v>
@@ -24132,6 +24127,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Kalkbrott 5 m NV.</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>127295455</v>
       </c>
       <c r="B217" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>127295429</v>
       </c>
       <c r="B218" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B219" t="n">
-        <v>107318</v>
+        <v>106735</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R219" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B220" t="n">
-        <v>106729</v>
+        <v>107324</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R220" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106729</v>
+        <v>106735</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102569</v>
+        <v>102575</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -22456,27 +22456,27 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126697989</v>
+        <v>126697541</v>
       </c>
       <c r="B200" t="n">
-        <v>106735</v>
+        <v>98470</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -22484,11 +22484,19 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L200" t="inlineStr"/>
@@ -22499,13 +22507,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>693831</v>
+        <v>693876</v>
       </c>
       <c r="R200" t="n">
-        <v>6360024</v>
+        <v>6360082</v>
       </c>
       <c r="S200" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22529,22 +22537,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>22:50</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>22:55</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22577,27 +22575,27 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126697541</v>
+        <v>126697989</v>
       </c>
       <c r="B201" t="n">
-        <v>98470</v>
+        <v>106735</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>219864</v>
+        <v>221849</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -22605,19 +22603,11 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L201" t="inlineStr"/>
@@ -22628,13 +22618,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>693876</v>
+        <v>693831</v>
       </c>
       <c r="R201" t="n">
-        <v>6360082</v>
+        <v>6360024</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22658,12 +22648,22 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23954,7 +23954,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127295453</v>
+        <v>127295426</v>
       </c>
       <c r="B213" t="n">
         <v>106735</v>
@@ -23989,7 +23989,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>693795</v>
+        <v>693766</v>
       </c>
       <c r="R213" t="n">
         <v>6360053</v>
@@ -24025,6 +24025,11 @@
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Kalkbrott 5 m NV.</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24056,7 +24061,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127295426</v>
+        <v>127295453</v>
       </c>
       <c r="B214" t="n">
         <v>106735</v>
@@ -24091,7 +24096,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>693766</v>
+        <v>693795</v>
       </c>
       <c r="R214" t="n">
         <v>6360053</v>
@@ -24127,11 +24132,6 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Kalkbrott 5 m NV.</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24367,10 +24367,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127295455</v>
+        <v>127295429</v>
       </c>
       <c r="B217" t="n">
-        <v>106735</v>
+        <v>109266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -24395,17 +24395,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693777</v>
+        <v>693796</v>
       </c>
       <c r="R217" t="n">
-        <v>6360032</v>
+        <v>6360056</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24438,11 +24447,6 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24474,10 +24478,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127295429</v>
+        <v>127295455</v>
       </c>
       <c r="B218" t="n">
-        <v>109266</v>
+        <v>106735</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24485,16 +24489,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -24502,26 +24506,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693796</v>
+        <v>693777</v>
       </c>
       <c r="R218" t="n">
-        <v>6360056</v>
+        <v>6360032</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24554,6 +24549,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B219" t="n">
-        <v>106735</v>
+        <v>107324</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R219" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B220" t="n">
-        <v>107324</v>
+        <v>106735</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R220" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -22459,7 +22459,7 @@
         <v>126697541</v>
       </c>
       <c r="B200" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>126697989</v>
       </c>
       <c r="B201" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>126697967</v>
       </c>
       <c r="B202" t="n">
-        <v>110323</v>
+        <v>110324</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>126697723</v>
       </c>
       <c r="B203" t="n">
-        <v>98417</v>
+        <v>98418</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>126697982</v>
       </c>
       <c r="B205" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23954,10 +23954,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127295426</v>
+        <v>127295453</v>
       </c>
       <c r="B213" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>693766</v>
+        <v>693795</v>
       </c>
       <c r="R213" t="n">
         <v>6360053</v>
@@ -24025,11 +24025,6 @@
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Kalkbrott 5 m NV.</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24061,10 +24056,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127295453</v>
+        <v>127295426</v>
       </c>
       <c r="B214" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24096,7 +24091,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>693795</v>
+        <v>693766</v>
       </c>
       <c r="R214" t="n">
         <v>6360053</v>
@@ -24132,6 +24127,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Kalkbrott 5 m NV.</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>127295429</v>
       </c>
       <c r="B217" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>127295455</v>
       </c>
       <c r="B218" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B219" t="n">
-        <v>107324</v>
+        <v>106736</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R219" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B220" t="n">
-        <v>106735</v>
+        <v>107325</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R220" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106735</v>
+        <v>106736</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102575</v>
+        <v>102576</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B219" t="n">
-        <v>106736</v>
+        <v>107325</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R219" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B220" t="n">
-        <v>107325</v>
+        <v>106736</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R220" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -22456,27 +22456,27 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126697541</v>
+        <v>126697989</v>
       </c>
       <c r="B200" t="n">
-        <v>98471</v>
+        <v>106736</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>219864</v>
+        <v>221849</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -22484,19 +22484,11 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L200" t="inlineStr"/>
@@ -22507,13 +22499,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>693876</v>
+        <v>693831</v>
       </c>
       <c r="R200" t="n">
-        <v>6360082</v>
+        <v>6360024</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22537,12 +22529,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-12</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22575,27 +22577,27 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126697989</v>
+        <v>126697541</v>
       </c>
       <c r="B201" t="n">
-        <v>106736</v>
+        <v>98471</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>221849</v>
+        <v>219864</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -22603,11 +22605,19 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L201" t="inlineStr"/>
@@ -22618,13 +22628,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>693831</v>
+        <v>693876</v>
       </c>
       <c r="R201" t="n">
-        <v>6360024</v>
+        <v>6360082</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22648,22 +22658,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>22:50</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>22:55</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23518,57 +23518,48 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127296656</v>
+        <v>127295449</v>
       </c>
       <c r="B209" t="n">
-        <v>57459</v>
+        <v>106736</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>102118</v>
+        <v>221849</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>693805</v>
+        <v>693796</v>
       </c>
       <c r="R209" t="n">
-        <v>6360191</v>
+        <v>6360105</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23598,11 +23589,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Uppskrämd från marken; trolig häckning i området.</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23634,48 +23620,57 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127295449</v>
+        <v>127296656</v>
       </c>
       <c r="B210" t="n">
-        <v>106736</v>
+        <v>57459</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>221849</v>
+        <v>102118</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>693796</v>
+        <v>693805</v>
       </c>
       <c r="R210" t="n">
-        <v>6360105</v>
+        <v>6360191</v>
       </c>
       <c r="S210" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23705,6 +23700,11 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken; trolig häckning i området.</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24367,10 +24367,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127295429</v>
+        <v>127295455</v>
       </c>
       <c r="B217" t="n">
-        <v>109267</v>
+        <v>106736</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -24395,26 +24395,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693796</v>
+        <v>693777</v>
       </c>
       <c r="R217" t="n">
-        <v>6360056</v>
+        <v>6360032</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24447,6 +24438,11 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24478,10 +24474,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127295455</v>
+        <v>127295429</v>
       </c>
       <c r="B218" t="n">
-        <v>106736</v>
+        <v>109267</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24489,16 +24485,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -24506,17 +24502,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693777</v>
+        <v>693796</v>
       </c>
       <c r="R218" t="n">
-        <v>6360032</v>
+        <v>6360056</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24549,11 +24554,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B219" t="n">
-        <v>107325</v>
+        <v>106736</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R219" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B220" t="n">
-        <v>106736</v>
+        <v>107325</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R220" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -24367,10 +24367,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127295455</v>
+        <v>127295429</v>
       </c>
       <c r="B217" t="n">
-        <v>106736</v>
+        <v>109267</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -24395,17 +24395,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693777</v>
+        <v>693796</v>
       </c>
       <c r="R217" t="n">
-        <v>6360032</v>
+        <v>6360056</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24438,11 +24447,6 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24474,10 +24478,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127295429</v>
+        <v>127295455</v>
       </c>
       <c r="B218" t="n">
-        <v>109267</v>
+        <v>106736</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24485,16 +24489,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -24502,26 +24506,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693796</v>
+        <v>693777</v>
       </c>
       <c r="R218" t="n">
-        <v>6360056</v>
+        <v>6360032</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24554,6 +24549,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD218" t="b">

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23518,48 +23518,57 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127295449</v>
+        <v>127296656</v>
       </c>
       <c r="B209" t="n">
-        <v>106736</v>
+        <v>57463</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221849</v>
+        <v>102118</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>693796</v>
+        <v>693805</v>
       </c>
       <c r="R209" t="n">
-        <v>6360105</v>
+        <v>6360191</v>
       </c>
       <c r="S209" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23589,6 +23598,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken; trolig häckning i området.</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23620,57 +23634,48 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127296656</v>
+        <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>57459</v>
+        <v>106742</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>102118</v>
+        <v>221849</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>693805</v>
+        <v>693796</v>
       </c>
       <c r="R210" t="n">
-        <v>6360191</v>
+        <v>6360105</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23700,11 +23705,6 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Uppskrämd från marken; trolig häckning i området.</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23954,10 +23954,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>127295453</v>
+        <v>127295426</v>
       </c>
       <c r="B213" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>693795</v>
+        <v>693766</v>
       </c>
       <c r="R213" t="n">
         <v>6360053</v>
@@ -24025,6 +24025,11 @@
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Kalkbrott 5 m NV.</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24056,10 +24061,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>127295426</v>
+        <v>127295453</v>
       </c>
       <c r="B214" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24091,7 +24096,7 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>693766</v>
+        <v>693795</v>
       </c>
       <c r="R214" t="n">
         <v>6360053</v>
@@ -24127,11 +24132,6 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Kalkbrott 5 m NV.</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>127295429</v>
       </c>
       <c r="B217" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>127295455</v>
       </c>
       <c r="B218" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B219" t="n">
-        <v>106736</v>
+        <v>107331</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R219" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B220" t="n">
-        <v>107325</v>
+        <v>106742</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R220" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106736</v>
+        <v>106742</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102576</v>
+        <v>102580</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B219" t="n">
-        <v>107331</v>
+        <v>106742</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R219" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B220" t="n">
-        <v>106742</v>
+        <v>107331</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R220" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -24367,10 +24367,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127295429</v>
+        <v>127295455</v>
       </c>
       <c r="B217" t="n">
-        <v>109273</v>
+        <v>106742</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -24395,26 +24395,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693796</v>
+        <v>693777</v>
       </c>
       <c r="R217" t="n">
-        <v>6360056</v>
+        <v>6360032</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24447,6 +24438,11 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24478,10 +24474,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127295455</v>
+        <v>127295429</v>
       </c>
       <c r="B218" t="n">
-        <v>106742</v>
+        <v>109273</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24489,16 +24485,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -24506,17 +24502,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693777</v>
+        <v>693796</v>
       </c>
       <c r="R218" t="n">
-        <v>6360032</v>
+        <v>6360056</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24549,11 +24554,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD218" t="b">

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>127295426</v>
       </c>
       <c r="B213" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>127295453</v>
       </c>
       <c r="B214" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24367,10 +24367,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127295455</v>
+        <v>127295429</v>
       </c>
       <c r="B217" t="n">
-        <v>106742</v>
+        <v>109275</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -24395,17 +24395,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693777</v>
+        <v>693796</v>
       </c>
       <c r="R217" t="n">
-        <v>6360032</v>
+        <v>6360056</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24438,11 +24447,6 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24474,10 +24478,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127295429</v>
+        <v>127295455</v>
       </c>
       <c r="B218" t="n">
-        <v>109273</v>
+        <v>106744</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24485,16 +24489,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -24502,26 +24506,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693796</v>
+        <v>693777</v>
       </c>
       <c r="R218" t="n">
-        <v>6360056</v>
+        <v>6360032</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24554,6 +24549,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B219" t="n">
-        <v>106742</v>
+        <v>107333</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R219" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B220" t="n">
-        <v>107331</v>
+        <v>106744</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R220" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106742</v>
+        <v>106744</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102580</v>
+        <v>102581</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23518,57 +23518,48 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127296656</v>
+        <v>127295449</v>
       </c>
       <c r="B209" t="n">
-        <v>57463</v>
+        <v>106746</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>102118</v>
+        <v>221849</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M209" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>693805</v>
+        <v>693796</v>
       </c>
       <c r="R209" t="n">
-        <v>6360191</v>
+        <v>6360105</v>
       </c>
       <c r="S209" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23598,11 +23589,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Uppskrämd från marken; trolig häckning i området.</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23634,48 +23620,57 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127295449</v>
+        <v>127296656</v>
       </c>
       <c r="B210" t="n">
-        <v>106744</v>
+        <v>57465</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>221849</v>
+        <v>102118</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>693796</v>
+        <v>693805</v>
       </c>
       <c r="R210" t="n">
-        <v>6360105</v>
+        <v>6360191</v>
       </c>
       <c r="S210" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23705,6 +23700,11 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken; trolig häckning i området.</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>127295426</v>
       </c>
       <c r="B213" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>127295453</v>
       </c>
       <c r="B214" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24367,10 +24367,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127295429</v>
+        <v>127295455</v>
       </c>
       <c r="B217" t="n">
-        <v>109275</v>
+        <v>106746</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -24395,26 +24395,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693796</v>
+        <v>693777</v>
       </c>
       <c r="R217" t="n">
-        <v>6360056</v>
+        <v>6360032</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24447,6 +24438,11 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24478,10 +24474,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127295455</v>
+        <v>127295429</v>
       </c>
       <c r="B218" t="n">
-        <v>106744</v>
+        <v>109277</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24489,16 +24485,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -24506,17 +24502,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693777</v>
+        <v>693796</v>
       </c>
       <c r="R218" t="n">
-        <v>6360032</v>
+        <v>6360056</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24549,11 +24554,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B219" t="n">
-        <v>107333</v>
+        <v>106746</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R219" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B220" t="n">
-        <v>106744</v>
+        <v>107335</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R220" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106744</v>
+        <v>106746</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102581</v>
+        <v>102583</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -23518,48 +23518,57 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127295449</v>
+        <v>127296656</v>
       </c>
       <c r="B209" t="n">
-        <v>106746</v>
+        <v>57465</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221849</v>
+        <v>102118</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P209" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>693796</v>
+        <v>693805</v>
       </c>
       <c r="R209" t="n">
-        <v>6360105</v>
+        <v>6360191</v>
       </c>
       <c r="S209" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -23589,6 +23598,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken; trolig häckning i området.</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23620,57 +23634,48 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>127296656</v>
+        <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>57465</v>
+        <v>106746</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>102118</v>
+        <v>221849</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>693805</v>
+        <v>693796</v>
       </c>
       <c r="R210" t="n">
-        <v>6360191</v>
+        <v>6360105</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23700,11 +23705,6 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Uppskrämd från marken; trolig häckning i området.</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24367,10 +24367,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127295455</v>
+        <v>127295429</v>
       </c>
       <c r="B217" t="n">
-        <v>106746</v>
+        <v>109277</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -24395,17 +24395,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693777</v>
+        <v>693796</v>
       </c>
       <c r="R217" t="n">
-        <v>6360032</v>
+        <v>6360056</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24438,11 +24447,6 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24474,10 +24478,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127295429</v>
+        <v>127295455</v>
       </c>
       <c r="B218" t="n">
-        <v>109277</v>
+        <v>106746</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24485,16 +24489,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -24502,26 +24506,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693796</v>
+        <v>693777</v>
       </c>
       <c r="R218" t="n">
-        <v>6360056</v>
+        <v>6360032</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24554,6 +24549,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD218" t="b">

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B219" t="n">
-        <v>106746</v>
+        <v>107335</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R219" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B220" t="n">
-        <v>107335</v>
+        <v>106746</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R220" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>127295426</v>
       </c>
       <c r="B213" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>127295453</v>
       </c>
       <c r="B214" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>127295429</v>
       </c>
       <c r="B217" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>127295455</v>
       </c>
       <c r="B218" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>127295432</v>
       </c>
       <c r="B219" t="n">
-        <v>107335</v>
+        <v>107341</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>127295447</v>
       </c>
       <c r="B220" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106746</v>
+        <v>106752</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102583</v>
+        <v>102589</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>127296656</v>
       </c>
       <c r="B209" t="n">
-        <v>57465</v>
+        <v>57468</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>127295426</v>
       </c>
       <c r="B213" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>127295453</v>
       </c>
       <c r="B214" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24367,10 +24367,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127295429</v>
+        <v>127295455</v>
       </c>
       <c r="B217" t="n">
-        <v>109283</v>
+        <v>106755</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -24395,26 +24395,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693796</v>
+        <v>693777</v>
       </c>
       <c r="R217" t="n">
-        <v>6360056</v>
+        <v>6360032</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24447,6 +24438,11 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24478,10 +24474,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127295455</v>
+        <v>127295429</v>
       </c>
       <c r="B218" t="n">
-        <v>106752</v>
+        <v>109286</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24489,16 +24485,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -24506,17 +24502,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693777</v>
+        <v>693796</v>
       </c>
       <c r="R218" t="n">
-        <v>6360032</v>
+        <v>6360056</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24549,11 +24554,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24588,7 +24588,7 @@
         <v>127295432</v>
       </c>
       <c r="B219" t="n">
-        <v>107341</v>
+        <v>107344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>127295447</v>
       </c>
       <c r="B220" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106752</v>
+        <v>106755</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102589</v>
+        <v>102592</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>127296656</v>
       </c>
       <c r="B209" t="n">
-        <v>57468</v>
+        <v>57474</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>127295426</v>
       </c>
       <c r="B213" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>127295453</v>
       </c>
       <c r="B214" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>127295455</v>
       </c>
       <c r="B217" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>127295429</v>
       </c>
       <c r="B218" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>127295432</v>
       </c>
       <c r="B219" t="n">
-        <v>107344</v>
+        <v>107352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>127295447</v>
       </c>
       <c r="B220" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106755</v>
+        <v>106763</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102592</v>
+        <v>102600</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>127295426</v>
       </c>
       <c r="B213" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>127295453</v>
       </c>
       <c r="B214" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24367,10 +24367,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127295455</v>
+        <v>127295429</v>
       </c>
       <c r="B217" t="n">
-        <v>106763</v>
+        <v>109295</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -24395,17 +24395,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693777</v>
+        <v>693796</v>
       </c>
       <c r="R217" t="n">
-        <v>6360032</v>
+        <v>6360056</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24438,11 +24447,6 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24474,10 +24478,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127295429</v>
+        <v>127295455</v>
       </c>
       <c r="B218" t="n">
-        <v>109294</v>
+        <v>106764</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24485,16 +24489,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -24502,26 +24506,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693796</v>
+        <v>693777</v>
       </c>
       <c r="R218" t="n">
-        <v>6360056</v>
+        <v>6360032</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24554,6 +24549,11 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B219" t="n">
-        <v>107352</v>
+        <v>106764</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R219" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B220" t="n">
-        <v>106763</v>
+        <v>107353</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R220" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106763</v>
+        <v>106764</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102600</v>
+        <v>102601</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B219" t="n">
-        <v>106764</v>
+        <v>107353</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R219" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B220" t="n">
-        <v>107353</v>
+        <v>106764</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R220" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109295</v>
+        <v>109296</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>127295426</v>
       </c>
       <c r="B213" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>127295453</v>
       </c>
       <c r="B214" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24367,10 +24367,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>127295429</v>
+        <v>127295455</v>
       </c>
       <c r="B217" t="n">
-        <v>109295</v>
+        <v>106765</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24378,16 +24378,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -24395,26 +24395,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>693796</v>
+        <v>693777</v>
       </c>
       <c r="R217" t="n">
-        <v>6360056</v>
+        <v>6360032</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -24447,6 +24438,11 @@
       <c r="AA217" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24478,10 +24474,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>127295455</v>
+        <v>127295429</v>
       </c>
       <c r="B218" t="n">
-        <v>106764</v>
+        <v>109296</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24489,16 +24485,16 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -24506,17 +24502,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Fröjel Puser 1:30 (16) A 9064-2024, Gtl</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>693777</v>
+        <v>693796</v>
       </c>
       <c r="R218" t="n">
-        <v>6360032</v>
+        <v>6360056</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -24549,11 +24554,6 @@
       <c r="AA218" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Kalkbrott i kalkbegskant mot väste.</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B219" t="n">
-        <v>107353</v>
+        <v>106765</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R219" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B220" t="n">
-        <v>106764</v>
+        <v>107354</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R220" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106764</v>
+        <v>106765</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102601</v>
+        <v>102602</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -22459,7 +22459,7 @@
         <v>126697989</v>
       </c>
       <c r="B200" t="n">
-        <v>106736</v>
+        <v>106729</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>126697541</v>
       </c>
       <c r="B201" t="n">
-        <v>98471</v>
+        <v>98464</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>126697967</v>
       </c>
       <c r="B202" t="n">
-        <v>110324</v>
+        <v>110317</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>126697723</v>
       </c>
       <c r="B203" t="n">
-        <v>98418</v>
+        <v>98411</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>126697982</v>
       </c>
       <c r="B205" t="n">
-        <v>98471</v>
+        <v>98464</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>127295445</v>
       </c>
       <c r="B207" t="n">
-        <v>106765</v>
+        <v>106729</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>127295652</v>
       </c>
       <c r="B208" t="n">
-        <v>106765</v>
+        <v>106729</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>127296656</v>
       </c>
       <c r="B209" t="n">
-        <v>57474</v>
+        <v>57459</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>127295449</v>
       </c>
       <c r="B210" t="n">
-        <v>106765</v>
+        <v>106729</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>127295427</v>
       </c>
       <c r="B211" t="n">
-        <v>109296</v>
+        <v>109260</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>127295437</v>
       </c>
       <c r="B212" t="n">
-        <v>106765</v>
+        <v>106729</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>127295426</v>
       </c>
       <c r="B213" t="n">
-        <v>106765</v>
+        <v>106729</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>127295453</v>
       </c>
       <c r="B214" t="n">
-        <v>106765</v>
+        <v>106729</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>127295436</v>
       </c>
       <c r="B215" t="n">
-        <v>106765</v>
+        <v>106729</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>127295442</v>
       </c>
       <c r="B216" t="n">
-        <v>106765</v>
+        <v>106729</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>127295455</v>
       </c>
       <c r="B217" t="n">
-        <v>106765</v>
+        <v>106729</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>127295429</v>
       </c>
       <c r="B218" t="n">
-        <v>109296</v>
+        <v>109260</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24585,10 +24585,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>127295447</v>
+        <v>127295432</v>
       </c>
       <c r="B219" t="n">
-        <v>106765</v>
+        <v>107318</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24596,31 +24596,31 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -24629,10 +24629,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>693788</v>
+        <v>693813</v>
       </c>
       <c r="R219" t="n">
-        <v>6360120</v>
+        <v>6360058</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -24696,10 +24696,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>127295432</v>
+        <v>127295447</v>
       </c>
       <c r="B220" t="n">
-        <v>107354</v>
+        <v>106729</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24707,31 +24707,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -24740,10 +24740,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693813</v>
+        <v>693788</v>
       </c>
       <c r="R220" t="n">
-        <v>6360058</v>
+        <v>6360120</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -24810,7 +24810,7 @@
         <v>127295440</v>
       </c>
       <c r="B221" t="n">
-        <v>106765</v>
+        <v>106729</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>127295443</v>
       </c>
       <c r="B222" t="n">
-        <v>102602</v>
+        <v>102569</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -26137,7 +26137,7 @@
         <v>129317452</v>
       </c>
       <c r="B244" t="n">
-        <v>103305</v>
+        <v>103385</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>

--- a/artfynd/A 9064-2024 artfynd.xlsx
+++ b/artfynd/A 9064-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY439"/>
+  <dimension ref="A1:AZ439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382896</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382897</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382898</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382899</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382900</t>
         </is>
       </c>
     </row>
@@ -1291,6 +1321,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389967</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389969</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389970</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393451</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393452</t>
         </is>
       </c>
     </row>
@@ -1826,6 +1881,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401510</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1931,6 +1991,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401511</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2036,6 +2101,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401512</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401513</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2246,6 +2321,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401514</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2351,6 +2431,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120471218</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2456,6 +2541,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120471219</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2561,6 +2651,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120471220</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2666,6 +2761,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120471221</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2767,6 +2867,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487301</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2868,6 +2973,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487303</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2969,6 +3079,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487304</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3070,6 +3185,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487306</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3171,6 +3291,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487308</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3272,6 +3397,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487310</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3373,6 +3503,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487312</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3474,6 +3609,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488153</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3575,6 +3715,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488211</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3676,6 +3821,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488212</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3786,6 +3936,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488870</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3894,6 +4049,11 @@
       <c r="AY32" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488871</t>
         </is>
       </c>
     </row>
@@ -4006,6 +4166,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382133</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4116,6 +4281,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389972</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4217,6 +4387,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487381</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4318,6 +4493,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382889</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4419,6 +4599,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393465</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4520,6 +4705,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393466</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4617,6 +4807,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434528</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4714,6 +4909,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434840</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4811,6 +5011,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434958</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4922,6 +5127,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122877286</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5033,6 +5243,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122877287</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5130,6 +5345,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893962</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5227,6 +5447,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893963</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5341,6 +5566,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382150</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5442,6 +5672,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382844</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5543,6 +5778,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382845</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5644,6 +5884,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382847</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5743,6 +5988,11 @@
       <c r="AY50" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382848</t>
         </is>
       </c>
     </row>
@@ -5859,6 +6109,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120390006</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5960,6 +6215,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393449</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6059,6 +6319,11 @@
       <c r="AY53" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393450</t>
         </is>
       </c>
     </row>
@@ -6166,6 +6431,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401489</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6271,6 +6541,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401490</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6372,6 +6647,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487278</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6482,6 +6762,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488867</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6592,6 +6877,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488868</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6702,6 +6992,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488869</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6803,6 +7098,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488194</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6900,6 +7200,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893977</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6997,6 +7302,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893978</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7094,6 +7404,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893979</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7191,6 +7506,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893980</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7288,6 +7608,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893981</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7385,6 +7710,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893982</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7482,6 +7812,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893983</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7583,6 +7918,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382857</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7684,6 +8024,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487323</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7783,6 +8128,11 @@
       <c r="AY70" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487325</t>
         </is>
       </c>
     </row>
@@ -7899,6 +8249,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382149</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8001,6 +8356,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286257</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8115,6 +8475,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382142</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8214,6 +8579,11 @@
       <c r="AY74" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382901</t>
         </is>
       </c>
     </row>
@@ -8321,6 +8691,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401500</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8426,6 +8801,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401515</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8523,6 +8903,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893993</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8620,6 +9005,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893994</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8734,6 +9124,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382130</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8850,6 +9245,11 @@
       <c r="AY80" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382131</t>
         </is>
       </c>
     </row>
@@ -8966,6 +9366,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382132</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9067,6 +9472,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382854</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9168,6 +9578,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382855</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9269,6 +9684,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382856</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9368,6 +9788,11 @@
       <c r="AY85" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382890</t>
         </is>
       </c>
     </row>
@@ -9484,6 +9909,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389965</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9598,6 +10028,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389966</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9699,6 +10134,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393467</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9799,6 +10239,11 @@
       <c r="AY89" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393468</t>
         </is>
       </c>
     </row>
@@ -9906,6 +10351,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401494</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10011,6 +10461,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120471225</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10116,6 +10571,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120471226</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10217,6 +10677,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487403</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10318,6 +10783,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487404</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10419,6 +10889,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487405</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10520,6 +10995,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488152</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10621,6 +11101,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488166</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10731,6 +11216,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488887</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10833,6 +11323,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286254</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10934,6 +11429,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382859</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11033,6 +11533,11 @@
       <c r="AY101" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393455</t>
         </is>
       </c>
     </row>
@@ -11140,6 +11645,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401495</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11237,6 +11747,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893988</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11351,6 +11866,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382147</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11465,6 +11985,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382148</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11579,6 +12104,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120390004</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11693,6 +12223,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120390005</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11794,6 +12329,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393448</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11895,6 +12435,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393454</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11992,6 +12537,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893990</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12106,6 +12656,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120390015</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12205,6 +12760,11 @@
       <c r="AY112" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382881</t>
         </is>
       </c>
     </row>
@@ -12312,6 +12872,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401492</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12423,6 +12988,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116114830</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12534,6 +13104,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116114833</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12635,6 +13210,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382853</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12736,6 +13316,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487320</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12848,6 +13433,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653172</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12967,6 +13557,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441955</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13086,6 +13681,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126441978</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13205,6 +13805,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126442250</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13329,6 +13934,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126697574</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13453,6 +14063,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126697599</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13560,6 +14175,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653139</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13667,6 +14287,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653146</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13774,6 +14399,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653147</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13881,6 +14511,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653148</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13993,6 +14628,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653149</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14100,6 +14740,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653151</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14207,6 +14852,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653152</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14314,6 +14964,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653153</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14421,6 +15076,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653155</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14528,6 +15188,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653156</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14640,6 +15305,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653157</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14747,6 +15417,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653159</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14854,6 +15529,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653160</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14966,6 +15646,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653162</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15073,6 +15758,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653163</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15180,6 +15870,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653164</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15287,6 +15982,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653165</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15394,6 +16094,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653167</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15501,6 +16206,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653169</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15608,6 +16318,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653171</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15715,6 +16430,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653173</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15822,6 +16542,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653174</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15929,6 +16654,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653176</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16041,6 +16771,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653177</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16153,6 +16888,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653178</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16260,6 +17000,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653179</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16367,6 +17112,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653180</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16474,6 +17224,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653181</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16581,6 +17336,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653182</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16688,6 +17448,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653183</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16800,6 +17565,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653185</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16907,6 +17677,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653186</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17019,6 +17794,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653187</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17126,6 +17906,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653189</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17233,6 +18018,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653190</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17340,6 +18130,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653191</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17452,6 +18247,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653192</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17559,6 +18359,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653193</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17666,6 +18471,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653194</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17778,6 +18588,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653195</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17885,6 +18700,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653196</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17997,6 +18817,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653197</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18109,6 +18934,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653199</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18221,6 +19051,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653200</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18333,6 +19168,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653204</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18440,6 +19280,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653205</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18547,6 +19392,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653207</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18654,6 +19504,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653208</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18761,6 +19616,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653209</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18868,6 +19728,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653210</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18975,6 +19840,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653211</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19082,6 +19952,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653212</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19189,6 +20064,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653215</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19296,6 +20176,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653216</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19403,6 +20288,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653217</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19510,6 +20400,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653218</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19617,6 +20512,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653219</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19724,6 +20624,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653220</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19831,6 +20736,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653221</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19938,6 +20848,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653222</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20045,6 +20960,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653224</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20152,6 +21072,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653225</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20259,6 +21184,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653226</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20366,6 +21296,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653227</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20473,6 +21408,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653228</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20580,6 +21520,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653229</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20687,6 +21632,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653230</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20794,6 +21744,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653231</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20901,6 +21856,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653232</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21008,6 +21968,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653235</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21115,6 +22080,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653238</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21222,6 +22192,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653239</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21329,6 +22304,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653241</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21436,6 +22416,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653243</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21543,6 +22528,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653244</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21655,6 +22645,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653246</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21762,6 +22757,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653247</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21869,6 +22869,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653248</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21976,6 +22981,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653249</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22083,6 +23093,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653250</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22190,6 +23205,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653251</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22302,6 +23322,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653252</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22414,6 +23439,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653253</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22521,6 +23551,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653254</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22628,6 +23663,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653255</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22735,6 +23775,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653256</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22842,6 +23887,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653257</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22949,6 +23999,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653258</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23061,6 +24116,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653260</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23168,6 +24228,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653262</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23275,6 +24340,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653263</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23393,6 +24463,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653264</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23500,6 +24575,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653267</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23607,6 +24687,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653268</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23714,6 +24799,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655767</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23821,6 +24911,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655768</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23928,6 +25023,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655770</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24035,6 +25135,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655771</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24142,6 +25247,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655772</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24249,6 +25359,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655774</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24356,6 +25471,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655776</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24468,6 +25588,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655777</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24575,6 +25700,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655779</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24687,6 +25817,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655782</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24799,6 +25934,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655783</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24911,6 +26051,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655787</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25023,6 +26168,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655788</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25130,6 +26280,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655790</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25237,6 +26392,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655792</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25344,6 +26504,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655794</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25451,6 +26616,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655796</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25563,6 +26733,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655798</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25670,6 +26845,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655800</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25782,6 +26962,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655802</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25889,6 +27074,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655803</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25996,6 +27186,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655804</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26103,6 +27298,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655805</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26210,6 +27410,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655807</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26317,6 +27522,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655808</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26424,6 +27634,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655809</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26531,6 +27746,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655811</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26638,6 +27858,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655812</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26745,6 +27970,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655813</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26852,6 +28082,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655815</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26959,6 +28194,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655816</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27066,6 +28306,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655817</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27173,6 +28418,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655818</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27280,6 +28530,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655820</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27387,6 +28642,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655821</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27499,6 +28759,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655824</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27606,6 +28871,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655825</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27713,6 +28983,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655826</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27825,6 +29100,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655827</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27932,6 +29212,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655829</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28044,6 +29329,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655830</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28151,6 +29441,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655831</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28258,6 +29553,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655832</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28370,6 +29670,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655833</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28477,6 +29782,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655835</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -28589,6 +29899,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655836</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -28696,6 +30011,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655838</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28808,6 +30128,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655839</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -28920,6 +30245,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655840</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29027,6 +30357,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655841</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29139,6 +30474,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134655842</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -29246,6 +30586,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657974</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29358,6 +30703,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657976</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -29465,6 +30815,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657977</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -29572,6 +30927,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657978</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -29684,6 +31044,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657980</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -29791,6 +31156,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657981</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -29903,6 +31273,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657982</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30010,6 +31385,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657983</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30117,6 +31497,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657986</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -30224,6 +31609,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657987</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -30336,6 +31726,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657988</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30448,6 +31843,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657989</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -30560,6 +31960,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657990</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -30667,6 +32072,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657991</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -30774,6 +32184,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657993</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -30881,6 +32296,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657994</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -30988,6 +32408,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657995</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31095,6 +32520,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657997</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31202,6 +32632,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657998</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -31309,6 +32744,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134657999</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -31421,6 +32861,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658000</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -31528,6 +32973,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658001</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -31635,6 +33085,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658002</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -31747,6 +33202,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658004</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -31854,6 +33314,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658005</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -31961,6 +33426,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658006</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32073,6 +33543,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658007</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32185,6 +33660,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658008</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -32292,6 +33772,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658009</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -32399,6 +33884,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658010</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -32511,6 +34001,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658011</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -32623,6 +34118,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658012</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -32735,6 +34235,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658014</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -32842,6 +34347,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658016</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -32949,6 +34459,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658018</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -33056,6 +34571,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658021</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -33168,6 +34688,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658022</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -33275,6 +34800,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658024</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -33382,6 +34912,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658026</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -33489,6 +35024,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658027</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -33596,6 +35136,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658028</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -33708,6 +35253,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658029</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -33832,6 +35382,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126697892</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -33943,6 +35498,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317469</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -34044,6 +35604,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487357</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -34150,6 +35715,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116114831</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -34252,6 +35822,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116110785</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -34354,6 +35929,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116113362</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -34456,6 +36036,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116113385</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -34555,6 +36140,11 @@
       <c r="AY318" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487353</t>
         </is>
       </c>
     </row>
@@ -34679,6 +36269,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126697967</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -34798,6 +36393,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126697723</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -34895,6 +36495,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893975</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -34996,6 +36601,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382865</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -35097,6 +36707,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382876</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -35198,6 +36813,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382877</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -35305,6 +36925,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134653237</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -35421,6 +37046,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116094955</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -35537,6 +37167,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116094976</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -35653,6 +37288,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116094986</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -35772,6 +37412,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126697541</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -35901,6 +37546,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126697982</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -36016,6 +37666,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120390026</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -36127,6 +37782,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317441</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -36224,6 +37884,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434061</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -36340,6 +38005,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317437</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -36451,6 +38121,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317439</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -36548,6 +38223,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893999</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -36650,6 +38330,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116094972</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -36752,6 +38437,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116094981</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -36854,6 +38544,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116094984</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -36969,6 +38664,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120390025</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -37090,6 +38790,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126697989</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -37197,6 +38902,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317436</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -37299,6 +39009,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317445</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -37401,6 +39116,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317446</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -37503,6 +39223,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317449</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -37605,6 +39330,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317451</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -37707,6 +39437,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317454</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -37818,6 +39553,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317456</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -37920,6 +39660,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317459</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -38022,6 +39767,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317461</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -38124,6 +39874,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317463</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -38231,6 +39986,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317465</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -38338,6 +40098,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116113449</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -38439,6 +40204,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487383</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -38540,6 +40310,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487384</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -38641,6 +40416,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487386</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -38742,6 +40522,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487387</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -38843,6 +40628,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487388</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -38944,6 +40734,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487389</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -39043,6 +40838,11 @@
       <c r="AY360" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487390</t>
         </is>
       </c>
     </row>
@@ -39151,6 +40951,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488890</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -39250,6 +41055,11 @@
       <c r="AY362" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488183</t>
         </is>
       </c>
     </row>
@@ -39366,6 +41176,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382145</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -39480,6 +41295,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382146</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -39581,6 +41401,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382891</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -39682,6 +41507,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382892</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -39783,6 +41613,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382893</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -39884,6 +41719,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382894</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -39983,6 +41823,11 @@
       <c r="AY369" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382895</t>
         </is>
       </c>
     </row>
@@ -40099,6 +41944,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120390001</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -40200,6 +42050,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393470</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -40301,6 +42156,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393472</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -40400,6 +42260,11 @@
       <c r="AY373" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393473</t>
         </is>
       </c>
     </row>
@@ -40507,6 +42372,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401509</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -40608,6 +42478,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487408</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -40709,6 +42584,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487409</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -40810,6 +42690,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487410</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -40910,6 +42795,11 @@
       <c r="AY378" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488197</t>
         </is>
       </c>
     </row>
@@ -41026,6 +42916,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389985</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -41128,6 +43023,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286255</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -41225,6 +43125,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96893991</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -41339,6 +43244,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382135</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -41453,6 +43363,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382136</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -41554,6 +43469,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382886</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -41653,6 +43573,11 @@
       <c r="AY385" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382888</t>
         </is>
       </c>
     </row>
@@ -41769,6 +43694,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389973</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -41883,6 +43813,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389974</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -41984,6 +43919,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393463</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -42083,6 +44023,11 @@
       <c r="AY389" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393464</t>
         </is>
       </c>
     </row>
@@ -42190,6 +44135,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401504</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -42295,6 +44245,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401505</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -42400,6 +44355,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401506</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -42505,6 +44465,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120471223</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -42610,6 +44575,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120471224</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -42711,6 +44681,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487372</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -42812,6 +44787,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487373</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -42913,6 +44893,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487374</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -43014,6 +44999,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487375</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -43115,6 +45105,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487376</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -43216,6 +45211,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488154</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -43324,6 +45324,11 @@
       <c r="AY401" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488883</t>
         </is>
       </c>
     </row>
@@ -43440,6 +45445,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382143</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -43541,6 +45551,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382860</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -43642,6 +45657,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382861</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -43743,6 +45763,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382862</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -43844,6 +45869,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382863</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -43943,6 +45973,11 @@
       <c r="AY407" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382864</t>
         </is>
       </c>
     </row>
@@ -44059,6 +46094,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389979</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -44173,6 +46213,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389980</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -44287,6 +46332,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389981</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -44401,6 +46451,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389982</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -44515,6 +46570,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389983</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -44629,6 +46689,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389984</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -44730,6 +46795,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393456</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -44831,6 +46901,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393457</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -44930,6 +47005,11 @@
       <c r="AY416" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120393458</t>
         </is>
       </c>
     </row>
@@ -45037,6 +47117,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401496</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -45142,6 +47227,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401497</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -45247,6 +47337,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401498</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -45352,6 +47447,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120401499</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -45453,6 +47553,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487345</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -45554,6 +47659,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487347</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -45655,6 +47765,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487349</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -45756,6 +47871,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487351</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -45858,6 +47978,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488168</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -45959,6 +48084,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488174</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -46060,6 +48190,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488175</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -46170,6 +48305,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488874</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -46280,6 +48420,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488875</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -46388,6 +48533,11 @@
       <c r="AY430" t="inlineStr">
         <is>
           <t>Naturhänsyns Gotlandsträff 2024</t>
+        </is>
+      </c>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120488876</t>
         </is>
       </c>
     </row>
@@ -46504,6 +48654,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120389977</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -46605,6 +48760,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487380</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -46721,6 +48881,11 @@
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129317452</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -46817,6 +48982,11 @@
       <c r="AY434" t="inlineStr">
         <is>
           <t>Kalkbarrianerna Gotland</t>
+        </is>
+      </c>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382858</t>
         </is>
       </c>
     </row>
@@ -46929,6 +49099,11 @@
           <t>Kalkbarrianerna Gotland</t>
         </is>
       </c>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120390020</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -47030,6 +49205,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120471222</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -47127,6 +49307,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487327</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -47224,6 +49409,11 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487329</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -47321,8 +49511,453 @@
           <t>Naturhänsyns Gotlandsträff 2024</t>
         </is>
       </c>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120487331</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>